--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330380</v>
+        <v>122330551</v>
       </c>
       <c r="B2" t="n">
-        <v>74686</v>
+        <v>100441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650859</v>
+        <v>650872</v>
       </c>
       <c r="R2" t="n">
-        <v>6673800</v>
+        <v>6673787</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330403</v>
+        <v>122330362</v>
       </c>
       <c r="B3" t="n">
-        <v>90779</v>
+        <v>57390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,26 +807,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,7 +846,7 @@
         <v>650925</v>
       </c>
       <c r="R3" t="n">
-        <v>6673688</v>
+        <v>6673848</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -868,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330384</v>
+        <v>122330401</v>
       </c>
       <c r="B4" t="n">
-        <v>80602</v>
+        <v>90779</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +931,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650810</v>
+        <v>650967</v>
       </c>
       <c r="R4" t="n">
-        <v>6673516</v>
+        <v>6673588</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -983,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330362</v>
+        <v>122330352</v>
       </c>
       <c r="B5" t="n">
         <v>57390</v>
@@ -1077,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650925</v>
+        <v>650928</v>
       </c>
       <c r="R5" t="n">
-        <v>6673848</v>
+        <v>6673572</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1112,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1273,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330550</v>
+        <v>122330354</v>
       </c>
       <c r="B7" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,31 +1290,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1317,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650914</v>
+        <v>650939</v>
       </c>
       <c r="R7" t="n">
-        <v>6673702</v>
+        <v>6673581</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1352,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122330329</v>
+        <v>122330332</v>
       </c>
       <c r="B8" t="n">
-        <v>5172</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,25 +1414,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102204</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1428,7 +1441,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1438,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650881</v>
+        <v>650886</v>
       </c>
       <c r="R8" t="n">
-        <v>6673739</v>
+        <v>6673750</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1473,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,7 +1496,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1631,7 +1644,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330551</v>
+        <v>122330550</v>
       </c>
       <c r="B10" t="n">
         <v>100441</v>
@@ -1675,10 +1688,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650872</v>
+        <v>650914</v>
       </c>
       <c r="R10" t="n">
-        <v>6673787</v>
+        <v>6673702</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1710,7 +1723,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1720,7 +1733,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330359</v>
+        <v>122330407</v>
       </c>
       <c r="B11" t="n">
-        <v>57390</v>
+        <v>91394</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,39 +1772,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1799,10 +1803,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650923</v>
+        <v>650944</v>
       </c>
       <c r="R11" t="n">
-        <v>6673842</v>
+        <v>6673706</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1834,7 +1838,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1844,7 +1848,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,10 +1875,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122330545</v>
+        <v>122330356</v>
       </c>
       <c r="B12" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,39 +1887,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1923,10 +1927,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650988</v>
+        <v>650930</v>
       </c>
       <c r="R12" t="n">
-        <v>6673679</v>
+        <v>6673590</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1958,7 +1962,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1968,7 +1972,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,10 +1999,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122330356</v>
+        <v>122330380</v>
       </c>
       <c r="B13" t="n">
-        <v>57390</v>
+        <v>74686</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,39 +2011,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2047,10 +2042,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650930</v>
+        <v>650859</v>
       </c>
       <c r="R13" t="n">
-        <v>6673590</v>
+        <v>6673800</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2082,7 +2077,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2092,7 +2087,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,10 +2114,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122330531</v>
+        <v>122330396</v>
       </c>
       <c r="B14" t="n">
-        <v>98175</v>
+        <v>90744</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2131,39 +2126,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2171,10 +2157,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650980</v>
+        <v>650952</v>
       </c>
       <c r="R14" t="n">
-        <v>6673689</v>
+        <v>6673856</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2206,7 +2192,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2216,7 +2202,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,10 +2229,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122330407</v>
+        <v>122330545</v>
       </c>
       <c r="B15" t="n">
-        <v>91394</v>
+        <v>98175</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2255,30 +2241,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2286,10 +2281,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650944</v>
+        <v>650988</v>
       </c>
       <c r="R15" t="n">
-        <v>6673706</v>
+        <v>6673679</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2321,7 +2316,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2331,7 +2326,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2358,10 +2353,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330401</v>
+        <v>122330384</v>
       </c>
       <c r="B16" t="n">
-        <v>90779</v>
+        <v>80602</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2374,21 +2369,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2401,10 +2396,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650967</v>
+        <v>650810</v>
       </c>
       <c r="R16" t="n">
-        <v>6673588</v>
+        <v>6673516</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2436,7 +2431,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2446,7 +2441,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2473,10 +2473,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122330352</v>
+        <v>122330329</v>
       </c>
       <c r="B17" t="n">
-        <v>57390</v>
+        <v>5172</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2489,33 +2489,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>102204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2525,10 +2522,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650928</v>
+        <v>650881</v>
       </c>
       <c r="R17" t="n">
-        <v>6673572</v>
+        <v>6673739</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2560,7 +2557,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2570,7 +2567,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2597,10 +2594,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122330332</v>
+        <v>122330403</v>
       </c>
       <c r="B18" t="n">
-        <v>5173</v>
+        <v>90779</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2609,36 +2606,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2646,10 +2637,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650886</v>
+        <v>650925</v>
       </c>
       <c r="R18" t="n">
-        <v>6673750</v>
+        <v>6673688</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2681,7 +2672,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2691,7 +2682,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2718,7 +2709,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330396</v>
+        <v>122330390</v>
       </c>
       <c r="B19" t="n">
         <v>90744</v>
@@ -2761,10 +2752,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650952</v>
+        <v>650923</v>
       </c>
       <c r="R19" t="n">
-        <v>6673856</v>
+        <v>6673571</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2796,7 +2787,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2806,7 +2797,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2833,10 +2824,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330390</v>
+        <v>122330531</v>
       </c>
       <c r="B20" t="n">
-        <v>90744</v>
+        <v>98175</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2845,30 +2836,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650923</v>
+        <v>650980</v>
       </c>
       <c r="R20" t="n">
-        <v>6673571</v>
+        <v>6673689</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2948,7 +2948,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122330354</v>
+        <v>122330359</v>
       </c>
       <c r="B21" t="n">
         <v>57390</v>
@@ -2990,7 +2990,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650939</v>
+        <v>650923</v>
       </c>
       <c r="R21" t="n">
-        <v>6673581</v>
+        <v>6673842</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -1278,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330354</v>
+        <v>122330337</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
+        <v>5193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,20 +1290,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1311,16 +1311,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1330,10 +1327,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650939</v>
+        <v>650804</v>
       </c>
       <c r="R7" t="n">
-        <v>6673581</v>
+        <v>6673534</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1365,7 +1362,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1372,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122330332</v>
+        <v>122330550</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>100441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,32 +1415,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1451,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650886</v>
+        <v>650914</v>
       </c>
       <c r="R8" t="n">
-        <v>6673750</v>
+        <v>6673702</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1486,7 +1478,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1488,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,10 +1515,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330337</v>
+        <v>122330354</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>57390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1535,20 +1527,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1556,13 +1548,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1572,10 +1567,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650804</v>
+        <v>650939</v>
       </c>
       <c r="R9" t="n">
-        <v>6673534</v>
+        <v>6673581</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1607,7 +1602,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1612,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,10 +1639,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330550</v>
+        <v>122330332</v>
       </c>
       <c r="B10" t="n">
-        <v>100441</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1660,27 +1655,32 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650914</v>
+        <v>650886</v>
       </c>
       <c r="R10" t="n">
-        <v>6673702</v>
+        <v>6673750</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330551</v>
+        <v>122330337</v>
       </c>
       <c r="B2" t="n">
-        <v>100441</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650872</v>
+        <v>650804</v>
       </c>
       <c r="R2" t="n">
-        <v>6673787</v>
+        <v>6673534</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330362</v>
+        <v>122330384</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>80603</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,35 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650925</v>
+        <v>650810</v>
       </c>
       <c r="R3" t="n">
-        <v>6673848</v>
+        <v>6673516</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +884,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330401</v>
+        <v>122330545</v>
       </c>
       <c r="B4" t="n">
-        <v>90779</v>
+        <v>98185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,30 +928,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -958,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650967</v>
+        <v>650988</v>
       </c>
       <c r="R4" t="n">
-        <v>6673588</v>
+        <v>6673679</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -993,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330352</v>
+        <v>122330396</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>90754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,39 +1052,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1082,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650928</v>
+        <v>650952</v>
       </c>
       <c r="R5" t="n">
-        <v>6673572</v>
+        <v>6673856</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1117,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330547</v>
+        <v>122330551</v>
       </c>
       <c r="B6" t="n">
-        <v>98175</v>
+        <v>100451</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,37 +1167,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1206,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650902</v>
+        <v>650872</v>
       </c>
       <c r="R6" t="n">
-        <v>6673754</v>
+        <v>6673787</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1241,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330337</v>
+        <v>122330403</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>90789</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,36 +1283,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1327,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650804</v>
+        <v>650925</v>
       </c>
       <c r="R7" t="n">
-        <v>6673534</v>
+        <v>6673688</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1362,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1372,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122330550</v>
+        <v>122330354</v>
       </c>
       <c r="B8" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,31 +1398,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1443,10 +1438,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650914</v>
+        <v>650939</v>
       </c>
       <c r="R8" t="n">
-        <v>6673702</v>
+        <v>6673581</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1478,7 +1473,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1488,7 +1483,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,7 +1510,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330354</v>
+        <v>122330362</v>
       </c>
       <c r="B9" t="n">
         <v>57390</v>
@@ -1557,7 +1552,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1567,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650939</v>
+        <v>650925</v>
       </c>
       <c r="R9" t="n">
-        <v>6673581</v>
+        <v>6673848</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1602,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1612,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1760,10 +1755,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330407</v>
+        <v>122330550</v>
       </c>
       <c r="B11" t="n">
-        <v>91394</v>
+        <v>100451</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,26 +1771,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1803,10 +1799,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650944</v>
+        <v>650914</v>
       </c>
       <c r="R11" t="n">
-        <v>6673706</v>
+        <v>6673702</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1838,7 +1834,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1848,7 +1844,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1875,7 +1871,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122330356</v>
+        <v>122330359</v>
       </c>
       <c r="B12" t="n">
         <v>57390</v>
@@ -1917,7 +1913,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1927,10 +1923,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650930</v>
+        <v>650923</v>
       </c>
       <c r="R12" t="n">
-        <v>6673590</v>
+        <v>6673842</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1962,7 +1958,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1972,7 +1968,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1999,10 +1995,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122330380</v>
+        <v>122330356</v>
       </c>
       <c r="B13" t="n">
-        <v>74686</v>
+        <v>57390</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2011,30 +2007,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2042,10 +2047,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650859</v>
+        <v>650930</v>
       </c>
       <c r="R13" t="n">
-        <v>6673800</v>
+        <v>6673590</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2077,7 +2082,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2087,7 +2092,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2114,10 +2119,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122330396</v>
+        <v>122330352</v>
       </c>
       <c r="B14" t="n">
-        <v>90744</v>
+        <v>57390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2126,30 +2131,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2157,10 +2171,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650952</v>
+        <v>650928</v>
       </c>
       <c r="R14" t="n">
-        <v>6673856</v>
+        <v>6673572</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2192,7 +2206,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2202,7 +2216,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2229,10 +2243,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122330545</v>
+        <v>122330407</v>
       </c>
       <c r="B15" t="n">
-        <v>98175</v>
+        <v>91404</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2241,39 +2255,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2281,10 +2286,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650988</v>
+        <v>650944</v>
       </c>
       <c r="R15" t="n">
-        <v>6673679</v>
+        <v>6673706</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2316,7 +2321,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2326,7 +2331,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,10 +2358,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330384</v>
+        <v>122330531</v>
       </c>
       <c r="B16" t="n">
-        <v>80602</v>
+        <v>98185</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2365,30 +2370,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2396,10 +2410,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650810</v>
+        <v>650980</v>
       </c>
       <c r="R16" t="n">
-        <v>6673516</v>
+        <v>6673689</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2431,7 +2445,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2441,12 +2455,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2473,10 +2482,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122330329</v>
+        <v>122330547</v>
       </c>
       <c r="B17" t="n">
-        <v>5172</v>
+        <v>98185</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2485,36 +2494,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102204</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2522,10 +2534,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650881</v>
+        <v>650902</v>
       </c>
       <c r="R17" t="n">
-        <v>6673739</v>
+        <v>6673754</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2557,7 +2569,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2567,7 +2579,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2594,10 +2606,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122330403</v>
+        <v>122330401</v>
       </c>
       <c r="B18" t="n">
-        <v>90779</v>
+        <v>90789</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2637,10 +2649,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650925</v>
+        <v>650967</v>
       </c>
       <c r="R18" t="n">
-        <v>6673688</v>
+        <v>6673588</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2672,7 +2684,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2682,7 +2694,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2709,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330390</v>
+        <v>122330329</v>
       </c>
       <c r="B19" t="n">
-        <v>90744</v>
+        <v>5172</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2721,30 +2733,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>102204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2752,10 +2770,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650923</v>
+        <v>650881</v>
       </c>
       <c r="R19" t="n">
-        <v>6673571</v>
+        <v>6673739</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2787,7 +2805,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2797,7 +2815,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2824,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330531</v>
+        <v>122330390</v>
       </c>
       <c r="B20" t="n">
-        <v>98175</v>
+        <v>90754</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2836,39 +2854,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2876,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650980</v>
+        <v>650923</v>
       </c>
       <c r="R20" t="n">
-        <v>6673689</v>
+        <v>6673571</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2911,7 +2920,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,7 +2930,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2948,10 +2957,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122330359</v>
+        <v>122330380</v>
       </c>
       <c r="B21" t="n">
-        <v>57390</v>
+        <v>74686</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2960,39 +2969,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650923</v>
+        <v>650859</v>
       </c>
       <c r="R21" t="n">
-        <v>6673842</v>
+        <v>6673800</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3075,7 +3075,7 @@
         <v>122330557</v>
       </c>
       <c r="B22" t="n">
-        <v>105280</v>
+        <v>105290</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330337</v>
+        <v>122330403</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>90789</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650804</v>
+        <v>650925</v>
       </c>
       <c r="R2" t="n">
-        <v>6673534</v>
+        <v>6673688</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330384</v>
+        <v>122330380</v>
       </c>
       <c r="B3" t="n">
-        <v>80603</v>
+        <v>74686</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650810</v>
+        <v>650859</v>
       </c>
       <c r="R3" t="n">
-        <v>6673516</v>
+        <v>6673800</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -874,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,12 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330545</v>
+        <v>122330332</v>
       </c>
       <c r="B4" t="n">
-        <v>98185</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,39 +917,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -968,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650988</v>
+        <v>650886</v>
       </c>
       <c r="R4" t="n">
-        <v>6673679</v>
+        <v>6673750</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1003,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330396</v>
+        <v>122330384</v>
       </c>
       <c r="B5" t="n">
-        <v>90754</v>
+        <v>80603</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650952</v>
+        <v>650810</v>
       </c>
       <c r="R5" t="n">
-        <v>6673856</v>
+        <v>6673516</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1118,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330551</v>
+        <v>122330396</v>
       </c>
       <c r="B6" t="n">
-        <v>100451</v>
+        <v>90754</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,27 +1162,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1199,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650872</v>
+        <v>650952</v>
       </c>
       <c r="R6" t="n">
-        <v>6673787</v>
+        <v>6673856</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1234,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330403</v>
+        <v>122330547</v>
       </c>
       <c r="B7" t="n">
-        <v>90789</v>
+        <v>98185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,30 +1273,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1314,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650925</v>
+        <v>650902</v>
       </c>
       <c r="R7" t="n">
-        <v>6673688</v>
+        <v>6673754</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1349,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122330354</v>
+        <v>122330407</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>91404</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,39 +1397,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1438,10 +1428,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650939</v>
+        <v>650944</v>
       </c>
       <c r="R8" t="n">
-        <v>6673581</v>
+        <v>6673706</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1473,7 +1463,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,7 +1473,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,7 +1500,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330362</v>
+        <v>122330356</v>
       </c>
       <c r="B9" t="n">
         <v>57390</v>
@@ -1562,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650925</v>
+        <v>650930</v>
       </c>
       <c r="R9" t="n">
-        <v>6673848</v>
+        <v>6673590</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1597,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1634,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330332</v>
+        <v>122330337</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>5193</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1650,21 +1640,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1673,7 +1663,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1683,10 +1673,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650886</v>
+        <v>650804</v>
       </c>
       <c r="R10" t="n">
-        <v>6673750</v>
+        <v>6673534</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1718,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1728,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330550</v>
+        <v>122330352</v>
       </c>
       <c r="B11" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1767,31 +1757,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1799,10 +1797,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650914</v>
+        <v>650928</v>
       </c>
       <c r="R11" t="n">
-        <v>6673702</v>
+        <v>6673572</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1834,7 +1832,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1844,7 +1842,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,10 +1869,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122330359</v>
+        <v>122330390</v>
       </c>
       <c r="B12" t="n">
-        <v>57390</v>
+        <v>90754</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,39 +1881,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1926,7 +1915,7 @@
         <v>650923</v>
       </c>
       <c r="R12" t="n">
-        <v>6673842</v>
+        <v>6673571</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1958,7 +1947,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1968,7 +1957,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122330356</v>
+        <v>122330329</v>
       </c>
       <c r="B13" t="n">
-        <v>57390</v>
+        <v>5172</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2011,33 +2000,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>102204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2047,10 +2033,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650930</v>
+        <v>650881</v>
       </c>
       <c r="R13" t="n">
-        <v>6673590</v>
+        <v>6673739</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2082,7 +2068,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2092,7 +2078,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,7 +2105,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122330352</v>
+        <v>122330359</v>
       </c>
       <c r="B14" t="n">
         <v>57390</v>
@@ -2161,7 +2147,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2171,10 +2157,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650928</v>
+        <v>650923</v>
       </c>
       <c r="R14" t="n">
-        <v>6673572</v>
+        <v>6673842</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2206,7 +2192,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2216,7 +2202,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,10 +2229,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122330407</v>
+        <v>122330401</v>
       </c>
       <c r="B15" t="n">
-        <v>91404</v>
+        <v>90789</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2255,25 +2241,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2286,10 +2272,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650944</v>
+        <v>650967</v>
       </c>
       <c r="R15" t="n">
-        <v>6673706</v>
+        <v>6673588</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2321,7 +2307,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2331,7 +2317,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2358,10 +2344,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330531</v>
+        <v>122330362</v>
       </c>
       <c r="B16" t="n">
-        <v>98185</v>
+        <v>57390</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2370,39 +2356,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2410,10 +2396,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650980</v>
+        <v>650925</v>
       </c>
       <c r="R16" t="n">
-        <v>6673689</v>
+        <v>6673848</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2445,7 +2431,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2455,7 +2441,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2482,10 +2468,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122330547</v>
+        <v>122330551</v>
       </c>
       <c r="B17" t="n">
-        <v>98185</v>
+        <v>100451</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2494,37 +2480,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2534,10 +2512,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650902</v>
+        <v>650872</v>
       </c>
       <c r="R17" t="n">
-        <v>6673754</v>
+        <v>6673787</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2569,7 +2547,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2579,7 +2557,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2606,10 +2584,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122330401</v>
+        <v>122330550</v>
       </c>
       <c r="B18" t="n">
-        <v>90789</v>
+        <v>100451</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2618,30 +2596,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2649,10 +2628,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650967</v>
+        <v>650914</v>
       </c>
       <c r="R18" t="n">
-        <v>6673588</v>
+        <v>6673702</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2684,7 +2663,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2694,7 +2673,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2721,10 +2700,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330329</v>
+        <v>122330531</v>
       </c>
       <c r="B19" t="n">
-        <v>5172</v>
+        <v>98185</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2733,36 +2712,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102204</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2770,10 +2752,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650881</v>
+        <v>650980</v>
       </c>
       <c r="R19" t="n">
-        <v>6673739</v>
+        <v>6673689</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2805,7 +2787,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2815,7 +2797,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,10 +2824,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330390</v>
+        <v>122330354</v>
       </c>
       <c r="B20" t="n">
-        <v>90754</v>
+        <v>57390</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2854,30 +2836,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2885,10 +2876,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650923</v>
+        <v>650939</v>
       </c>
       <c r="R20" t="n">
-        <v>6673571</v>
+        <v>6673581</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2920,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2930,7 +2921,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2957,10 +2948,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122330380</v>
+        <v>122330545</v>
       </c>
       <c r="B21" t="n">
-        <v>74686</v>
+        <v>98185</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2969,30 +2960,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650859</v>
+        <v>650988</v>
       </c>
       <c r="R21" t="n">
-        <v>6673800</v>
+        <v>6673679</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330403</v>
+        <v>122330531</v>
       </c>
       <c r="B2" t="n">
-        <v>90789</v>
+        <v>98197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650925</v>
+        <v>650980</v>
       </c>
       <c r="R2" t="n">
-        <v>6673688</v>
+        <v>6673689</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330380</v>
+        <v>122330401</v>
       </c>
       <c r="B3" t="n">
-        <v>74686</v>
+        <v>90801</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +811,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650859</v>
+        <v>650967</v>
       </c>
       <c r="R3" t="n">
-        <v>6673800</v>
+        <v>6673588</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -868,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1026,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330384</v>
+        <v>122330356</v>
       </c>
       <c r="B5" t="n">
-        <v>80603</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,26 +1051,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650810</v>
+        <v>650930</v>
       </c>
       <c r="R5" t="n">
-        <v>6673516</v>
+        <v>6673590</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1104,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330396</v>
+        <v>122330337</v>
       </c>
       <c r="B6" t="n">
-        <v>90754</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,26 +1175,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1189,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650952</v>
+        <v>650804</v>
       </c>
       <c r="R6" t="n">
-        <v>6673856</v>
+        <v>6673534</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1224,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330547</v>
+        <v>122330384</v>
       </c>
       <c r="B7" t="n">
-        <v>98185</v>
+        <v>80608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,39 +1292,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1313,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650902</v>
+        <v>650810</v>
       </c>
       <c r="R7" t="n">
-        <v>6673754</v>
+        <v>6673516</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1348,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1368,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122330407</v>
+        <v>122330362</v>
       </c>
       <c r="B8" t="n">
-        <v>91404</v>
+        <v>57395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,30 +1412,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1428,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650944</v>
+        <v>650925</v>
       </c>
       <c r="R8" t="n">
-        <v>6673706</v>
+        <v>6673848</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1463,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1473,7 +1497,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1500,10 +1524,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330356</v>
+        <v>122330354</v>
       </c>
       <c r="B9" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,7 +1566,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1552,10 +1576,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650930</v>
+        <v>650939</v>
       </c>
       <c r="R9" t="n">
-        <v>6673590</v>
+        <v>6673581</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1587,7 +1611,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1621,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,10 +1648,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330337</v>
+        <v>122330407</v>
       </c>
       <c r="B10" t="n">
-        <v>5193</v>
+        <v>91416</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,32 +1664,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1673,10 +1691,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650804</v>
+        <v>650944</v>
       </c>
       <c r="R10" t="n">
-        <v>6673534</v>
+        <v>6673706</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1708,7 +1726,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1736,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,7 +1766,7 @@
         <v>122330352</v>
       </c>
       <c r="B11" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1869,10 +1887,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122330390</v>
+        <v>122330550</v>
       </c>
       <c r="B12" t="n">
-        <v>90754</v>
+        <v>100463</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,26 +1903,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1912,10 +1931,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650923</v>
+        <v>650914</v>
       </c>
       <c r="R12" t="n">
-        <v>6673571</v>
+        <v>6673702</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1947,7 +1966,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1957,7 +1976,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,10 +2003,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122330329</v>
+        <v>122330359</v>
       </c>
       <c r="B13" t="n">
-        <v>5172</v>
+        <v>57395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2000,30 +2019,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102204</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2033,10 +2055,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650881</v>
+        <v>650923</v>
       </c>
       <c r="R13" t="n">
-        <v>6673739</v>
+        <v>6673842</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2068,7 +2090,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2078,7 +2100,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2105,10 +2127,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122330359</v>
+        <v>122330396</v>
       </c>
       <c r="B14" t="n">
-        <v>57390</v>
+        <v>90766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2117,39 +2139,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2157,10 +2170,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650923</v>
+        <v>650952</v>
       </c>
       <c r="R14" t="n">
-        <v>6673842</v>
+        <v>6673856</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2192,7 +2205,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2202,7 +2215,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2229,10 +2242,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122330401</v>
+        <v>122330390</v>
       </c>
       <c r="B15" t="n">
-        <v>90789</v>
+        <v>90766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2241,25 +2254,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2272,10 +2285,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650967</v>
+        <v>650923</v>
       </c>
       <c r="R15" t="n">
-        <v>6673588</v>
+        <v>6673571</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2307,7 +2320,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2317,7 +2330,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,10 +2357,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330362</v>
+        <v>122330547</v>
       </c>
       <c r="B16" t="n">
-        <v>57390</v>
+        <v>98197</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2356,39 +2369,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2396,10 +2409,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650925</v>
+        <v>650902</v>
       </c>
       <c r="R16" t="n">
-        <v>6673848</v>
+        <v>6673754</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2431,7 +2444,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2441,7 +2454,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2468,10 +2481,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122330551</v>
+        <v>122330545</v>
       </c>
       <c r="B17" t="n">
-        <v>100451</v>
+        <v>98197</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2480,29 +2493,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2512,10 +2533,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650872</v>
+        <v>650988</v>
       </c>
       <c r="R17" t="n">
-        <v>6673787</v>
+        <v>6673679</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2547,7 +2568,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2557,7 +2578,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2584,10 +2605,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122330550</v>
+        <v>122330380</v>
       </c>
       <c r="B18" t="n">
-        <v>100451</v>
+        <v>74691</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2600,27 +2621,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2628,10 +2648,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650914</v>
+        <v>650859</v>
       </c>
       <c r="R18" t="n">
-        <v>6673702</v>
+        <v>6673800</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2663,7 +2683,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2673,7 +2693,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2700,10 +2720,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330531</v>
+        <v>122330403</v>
       </c>
       <c r="B19" t="n">
-        <v>98185</v>
+        <v>90801</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2712,39 +2732,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2752,10 +2763,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650980</v>
+        <v>650925</v>
       </c>
       <c r="R19" t="n">
-        <v>6673689</v>
+        <v>6673688</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2787,7 +2798,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2797,7 +2808,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2824,10 +2835,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330354</v>
+        <v>122330329</v>
       </c>
       <c r="B20" t="n">
-        <v>57390</v>
+        <v>5172</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2840,33 +2851,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>102204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2876,10 +2884,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650939</v>
+        <v>650881</v>
       </c>
       <c r="R20" t="n">
-        <v>6673581</v>
+        <v>6673739</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2911,7 +2919,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,7 +2929,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2948,10 +2956,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122330545</v>
+        <v>122330551</v>
       </c>
       <c r="B21" t="n">
-        <v>98185</v>
+        <v>100463</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2960,37 +2968,29 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650988</v>
+        <v>650872</v>
       </c>
       <c r="R21" t="n">
-        <v>6673679</v>
+        <v>6673787</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3075,7 +3075,7 @@
         <v>122330557</v>
       </c>
       <c r="B22" t="n">
-        <v>105290</v>
+        <v>105303</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330531</v>
+        <v>122330401</v>
       </c>
       <c r="B2" t="n">
-        <v>98197</v>
+        <v>90808</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650980</v>
+        <v>650967</v>
       </c>
       <c r="R2" t="n">
-        <v>6673689</v>
+        <v>6673588</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330401</v>
+        <v>122330352</v>
       </c>
       <c r="B3" t="n">
-        <v>90801</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,26 +806,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650967</v>
+        <v>650928</v>
       </c>
       <c r="R3" t="n">
-        <v>6673588</v>
+        <v>6673572</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330332</v>
+        <v>122330384</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>80608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,36 +926,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650886</v>
+        <v>650810</v>
       </c>
       <c r="R4" t="n">
-        <v>6673750</v>
+        <v>6673516</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -998,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1002,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330356</v>
+        <v>122330332</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,37 +1046,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1087,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650930</v>
+        <v>650886</v>
       </c>
       <c r="R5" t="n">
-        <v>6673590</v>
+        <v>6673750</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1122,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330337</v>
+        <v>122330407</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>91421</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,32 +1171,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1208,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650804</v>
+        <v>650944</v>
       </c>
       <c r="R6" t="n">
-        <v>6673534</v>
+        <v>6673706</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1243,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330384</v>
+        <v>122330359</v>
       </c>
       <c r="B7" t="n">
-        <v>80608</v>
+        <v>57395</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,26 +1286,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1323,10 +1322,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650810</v>
+        <v>650923</v>
       </c>
       <c r="R7" t="n">
-        <v>6673516</v>
+        <v>6673842</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1358,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,12 +1367,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,7 +1394,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122330362</v>
+        <v>122330354</v>
       </c>
       <c r="B8" t="n">
         <v>57395</v>
@@ -1442,7 +1436,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1452,10 +1446,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650925</v>
+        <v>650939</v>
       </c>
       <c r="R8" t="n">
-        <v>6673848</v>
+        <v>6673581</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1487,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,7 +1491,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330354</v>
+        <v>122330547</v>
       </c>
       <c r="B9" t="n">
-        <v>57395</v>
+        <v>98202</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1536,39 +1530,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1576,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650939</v>
+        <v>650902</v>
       </c>
       <c r="R9" t="n">
-        <v>6673581</v>
+        <v>6673754</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1611,7 +1605,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1621,7 +1615,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,10 +1642,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330407</v>
+        <v>122330403</v>
       </c>
       <c r="B10" t="n">
-        <v>91416</v>
+        <v>90808</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1660,25 +1654,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1691,10 +1685,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650944</v>
+        <v>650925</v>
       </c>
       <c r="R10" t="n">
-        <v>6673706</v>
+        <v>6673688</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1726,7 +1720,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1736,7 +1730,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1763,10 +1757,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330352</v>
+        <v>122330396</v>
       </c>
       <c r="B11" t="n">
-        <v>57395</v>
+        <v>90773</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,39 +1769,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1815,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650928</v>
+        <v>650952</v>
       </c>
       <c r="R11" t="n">
-        <v>6673572</v>
+        <v>6673856</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1850,7 +1835,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1860,7 +1845,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,10 +1872,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122330550</v>
+        <v>122330329</v>
       </c>
       <c r="B12" t="n">
-        <v>100463</v>
+        <v>5172</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1899,31 +1884,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>102204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1931,10 +1921,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650914</v>
+        <v>650881</v>
       </c>
       <c r="R12" t="n">
-        <v>6673702</v>
+        <v>6673739</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1966,7 +1956,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1976,7 +1966,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2003,7 +1993,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122330359</v>
+        <v>122330356</v>
       </c>
       <c r="B13" t="n">
         <v>57395</v>
@@ -2045,7 +2035,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2055,10 +2045,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650923</v>
+        <v>650930</v>
       </c>
       <c r="R13" t="n">
-        <v>6673842</v>
+        <v>6673590</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2090,7 +2080,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2100,7 +2090,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2127,10 +2117,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122330396</v>
+        <v>122330545</v>
       </c>
       <c r="B14" t="n">
-        <v>90766</v>
+        <v>98202</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2139,30 +2129,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2170,10 +2169,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650952</v>
+        <v>650988</v>
       </c>
       <c r="R14" t="n">
-        <v>6673856</v>
+        <v>6673679</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2205,7 +2204,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2215,7 +2214,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2245,7 +2244,7 @@
         <v>122330390</v>
       </c>
       <c r="B15" t="n">
-        <v>90766</v>
+        <v>90773</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2357,10 +2356,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330547</v>
+        <v>122330550</v>
       </c>
       <c r="B16" t="n">
-        <v>98197</v>
+        <v>100468</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2369,37 +2368,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2409,10 +2400,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650902</v>
+        <v>650914</v>
       </c>
       <c r="R16" t="n">
-        <v>6673754</v>
+        <v>6673702</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2444,7 +2435,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2454,7 +2445,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2481,10 +2472,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122330545</v>
+        <v>122330551</v>
       </c>
       <c r="B17" t="n">
-        <v>98197</v>
+        <v>100468</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2493,37 +2484,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2533,10 +2516,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650988</v>
+        <v>650872</v>
       </c>
       <c r="R17" t="n">
-        <v>6673679</v>
+        <v>6673787</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2568,7 +2551,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2578,7 +2561,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2720,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330403</v>
+        <v>122330337</v>
       </c>
       <c r="B19" t="n">
-        <v>90801</v>
+        <v>5193</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2732,30 +2715,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2763,10 +2752,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650925</v>
+        <v>650804</v>
       </c>
       <c r="R19" t="n">
-        <v>6673688</v>
+        <v>6673534</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2798,7 +2787,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2808,7 +2797,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2835,10 +2824,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330329</v>
+        <v>122330531</v>
       </c>
       <c r="B20" t="n">
-        <v>5172</v>
+        <v>98202</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2847,36 +2836,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102204</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2884,10 +2876,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650881</v>
+        <v>650980</v>
       </c>
       <c r="R20" t="n">
-        <v>6673739</v>
+        <v>6673689</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2919,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2929,7 +2921,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2956,10 +2948,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122330551</v>
+        <v>122330362</v>
       </c>
       <c r="B21" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2968,31 +2960,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650872</v>
+        <v>650925</v>
       </c>
       <c r="R21" t="n">
-        <v>6673787</v>
+        <v>6673848</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3075,7 +3075,7 @@
         <v>122330557</v>
       </c>
       <c r="B22" t="n">
-        <v>105303</v>
+        <v>105308</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -1518,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330547</v>
+        <v>122330396</v>
       </c>
       <c r="B9" t="n">
-        <v>98202</v>
+        <v>90773</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,39 +1530,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1570,10 +1561,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650902</v>
+        <v>650952</v>
       </c>
       <c r="R9" t="n">
-        <v>6673754</v>
+        <v>6673856</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1605,7 +1596,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1615,7 +1606,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1757,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330396</v>
+        <v>122330547</v>
       </c>
       <c r="B11" t="n">
-        <v>90773</v>
+        <v>98202</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1769,30 +1760,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650952</v>
+        <v>650902</v>
       </c>
       <c r="R11" t="n">
-        <v>6673856</v>
+        <v>6673754</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2703,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330337</v>
+        <v>122330531</v>
       </c>
       <c r="B19" t="n">
-        <v>5193</v>
+        <v>98202</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2715,36 +2715,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2752,10 +2755,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650804</v>
+        <v>650980</v>
       </c>
       <c r="R19" t="n">
-        <v>6673534</v>
+        <v>6673689</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2787,7 +2790,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2797,7 +2800,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2824,10 +2827,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330531</v>
+        <v>122330337</v>
       </c>
       <c r="B20" t="n">
-        <v>98202</v>
+        <v>5193</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2836,39 +2839,36 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650980</v>
+        <v>650804</v>
       </c>
       <c r="R20" t="n">
-        <v>6673689</v>
+        <v>6673534</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330401</v>
+        <v>122330390</v>
       </c>
       <c r="B2" t="n">
-        <v>90808</v>
+        <v>90778</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>5447</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650967</v>
+        <v>650923</v>
       </c>
       <c r="R2" t="n">
-        <v>6673588</v>
+        <v>6673571</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330352</v>
+        <v>122330550</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +797,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650928</v>
+        <v>650914</v>
       </c>
       <c r="R3" t="n">
-        <v>6673572</v>
+        <v>6673702</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +859,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +869,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330384</v>
+        <v>122330352</v>
       </c>
       <c r="B4" t="n">
-        <v>80608</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,26 +912,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650810</v>
+        <v>650928</v>
       </c>
       <c r="R4" t="n">
-        <v>6673516</v>
+        <v>6673572</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -992,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,12 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330332</v>
+        <v>122330547</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>98211</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,36 +1027,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1083,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650886</v>
+        <v>650902</v>
       </c>
       <c r="R5" t="n">
-        <v>6673750</v>
+        <v>6673754</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1118,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1107,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330407</v>
+        <v>122330380</v>
       </c>
       <c r="B6" t="n">
-        <v>91421</v>
+        <v>74692</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,21 +1150,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Brandticka</t>
-        </is>
+        <v>6426</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650944</v>
+        <v>650859</v>
       </c>
       <c r="R6" t="n">
-        <v>6673706</v>
+        <v>6673800</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1233,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,11 +1262,6 @@
       <c r="E7" t="n">
         <v>100049</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1394,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122330354</v>
+        <v>122330551</v>
       </c>
       <c r="B8" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,39 +1375,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1446,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650939</v>
+        <v>650872</v>
       </c>
       <c r="R8" t="n">
-        <v>6673581</v>
+        <v>6673787</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1481,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330396</v>
+        <v>122330332</v>
       </c>
       <c r="B9" t="n">
-        <v>90773</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,26 +1490,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>100526</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1561,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650952</v>
+        <v>650886</v>
       </c>
       <c r="R9" t="n">
-        <v>6673856</v>
+        <v>6673750</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1596,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1606,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330403</v>
+        <v>122330384</v>
       </c>
       <c r="B10" t="n">
-        <v>90808</v>
+        <v>80609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,21 +1606,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>1049</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1676,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650925</v>
+        <v>650810</v>
       </c>
       <c r="R10" t="n">
-        <v>6673688</v>
+        <v>6673516</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1711,7 +1663,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1721,7 +1673,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330547</v>
+        <v>122330396</v>
       </c>
       <c r="B11" t="n">
-        <v>98202</v>
+        <v>90778</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,39 +1717,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5447</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1800,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650902</v>
+        <v>650952</v>
       </c>
       <c r="R11" t="n">
-        <v>6673754</v>
+        <v>6673856</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1835,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1845,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1872,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122330329</v>
+        <v>122330362</v>
       </c>
       <c r="B12" t="n">
-        <v>5172</v>
+        <v>57395</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1888,30 +1831,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102204</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Grönhjon</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1921,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650881</v>
+        <v>650925</v>
       </c>
       <c r="R12" t="n">
-        <v>6673739</v>
+        <v>6673848</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1956,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1966,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1993,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122330356</v>
+        <v>122330337</v>
       </c>
       <c r="B13" t="n">
-        <v>57395</v>
+        <v>5193</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2005,20 +1946,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>105930</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2026,16 +1962,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2045,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650930</v>
+        <v>650804</v>
       </c>
       <c r="R13" t="n">
-        <v>6673590</v>
+        <v>6673534</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2080,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2090,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2117,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122330545</v>
+        <v>122330531</v>
       </c>
       <c r="B14" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,11 +2068,6 @@
       <c r="E14" t="n">
         <v>220787</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2152,12 +2080,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2169,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650988</v>
+        <v>650980</v>
       </c>
       <c r="R14" t="n">
-        <v>6673679</v>
+        <v>6673689</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2204,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2214,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2241,10 +2169,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122330390</v>
+        <v>122330407</v>
       </c>
       <c r="B15" t="n">
-        <v>90773</v>
+        <v>91426</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2257,21 +2185,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>1339</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2284,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650923</v>
+        <v>650944</v>
       </c>
       <c r="R15" t="n">
-        <v>6673571</v>
+        <v>6673706</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2319,7 +2242,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2329,7 +2252,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2356,10 +2279,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330550</v>
+        <v>122330329</v>
       </c>
       <c r="B16" t="n">
-        <v>100468</v>
+        <v>5172</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2368,31 +2291,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>102204</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2400,10 +2323,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650914</v>
+        <v>650881</v>
       </c>
       <c r="R16" t="n">
-        <v>6673702</v>
+        <v>6673739</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2435,7 +2358,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2445,7 +2368,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,10 +2395,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122330551</v>
+        <v>122330545</v>
       </c>
       <c r="B17" t="n">
-        <v>100468</v>
+        <v>98211</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2484,29 +2407,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2516,10 +2442,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650872</v>
+        <v>650988</v>
       </c>
       <c r="R17" t="n">
-        <v>6673787</v>
+        <v>6673679</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2551,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2561,7 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2588,10 +2514,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122330380</v>
+        <v>122330403</v>
       </c>
       <c r="B18" t="n">
-        <v>74691</v>
+        <v>90813</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2600,25 +2526,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2631,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650859</v>
+        <v>650925</v>
       </c>
       <c r="R18" t="n">
-        <v>6673800</v>
+        <v>6673688</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2666,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2676,7 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2703,10 +2624,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330531</v>
+        <v>122330354</v>
       </c>
       <c r="B19" t="n">
-        <v>98202</v>
+        <v>57395</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2715,39 +2636,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2755,10 +2671,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650980</v>
+        <v>650939</v>
       </c>
       <c r="R19" t="n">
-        <v>6673689</v>
+        <v>6673581</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2790,7 +2706,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2800,7 +2716,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2827,10 +2743,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330337</v>
+        <v>122330401</v>
       </c>
       <c r="B20" t="n">
-        <v>5193</v>
+        <v>90813</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2839,36 +2755,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2876,10 +2781,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650804</v>
+        <v>650967</v>
       </c>
       <c r="R20" t="n">
-        <v>6673534</v>
+        <v>6673588</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2911,7 +2816,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,7 +2826,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2948,7 +2853,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122330362</v>
+        <v>122330356</v>
       </c>
       <c r="B21" t="n">
         <v>57395</v>
@@ -2965,11 +2870,6 @@
       </c>
       <c r="E21" t="n">
         <v>100049</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3000,10 +2900,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650925</v>
+        <v>650930</v>
       </c>
       <c r="R21" t="n">
-        <v>6673848</v>
+        <v>6673590</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3035,7 +2935,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3045,7 +2945,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3075,7 +2975,7 @@
         <v>122330557</v>
       </c>
       <c r="B22" t="n">
-        <v>105308</v>
+        <v>105317</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3089,11 +2989,6 @@
       </c>
       <c r="E22" t="n">
         <v>221144</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330390</v>
+        <v>122330545</v>
       </c>
       <c r="B2" t="n">
-        <v>90778</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>220787</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650923</v>
+        <v>650988</v>
       </c>
       <c r="R2" t="n">
-        <v>6673571</v>
+        <v>6673679</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -748,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330550</v>
+        <v>122330401</v>
       </c>
       <c r="B3" t="n">
-        <v>100477</v>
+        <v>90826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650914</v>
+        <v>650967</v>
       </c>
       <c r="R3" t="n">
-        <v>6673702</v>
+        <v>6673588</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -859,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330352</v>
+        <v>122330547</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>98224</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,34 +926,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650928</v>
+        <v>650902</v>
       </c>
       <c r="R4" t="n">
-        <v>6673572</v>
+        <v>6673754</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -978,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330547</v>
+        <v>122330356</v>
       </c>
       <c r="B5" t="n">
-        <v>98211</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1050,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650902</v>
+        <v>650930</v>
       </c>
       <c r="R5" t="n">
-        <v>6673754</v>
+        <v>6673590</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1097,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,7 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330380</v>
+        <v>122330352</v>
       </c>
       <c r="B6" t="n">
-        <v>74692</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,25 +1174,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650859</v>
+        <v>650928</v>
       </c>
       <c r="R6" t="n">
-        <v>6673800</v>
+        <v>6673572</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1207,7 +1249,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1259,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1286,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330359</v>
+        <v>122330550</v>
       </c>
       <c r="B7" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1298,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1291,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650923</v>
+        <v>650914</v>
       </c>
       <c r="R7" t="n">
-        <v>6673842</v>
+        <v>6673702</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1326,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,7 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122330551</v>
+        <v>122330354</v>
       </c>
       <c r="B8" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,26 +1414,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1402,10 +1454,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650872</v>
+        <v>650939</v>
       </c>
       <c r="R8" t="n">
-        <v>6673787</v>
+        <v>6673581</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1437,7 +1489,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1499,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1526,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330332</v>
+        <v>122330329</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>5172</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,20 +1538,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>102204</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,7 +1565,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1518,10 +1575,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650886</v>
+        <v>650881</v>
       </c>
       <c r="R9" t="n">
-        <v>6673750</v>
+        <v>6673739</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1553,7 +1610,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1620,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1647,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330384</v>
+        <v>122330380</v>
       </c>
       <c r="B10" t="n">
-        <v>80609</v>
+        <v>74696</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,20 +1659,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1049</v>
+        <v>6426</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1628,10 +1690,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650810</v>
+        <v>650859</v>
       </c>
       <c r="R10" t="n">
-        <v>6673516</v>
+        <v>6673800</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1663,7 +1725,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1673,12 +1735,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,7 +1765,7 @@
         <v>122330396</v>
       </c>
       <c r="B11" t="n">
-        <v>90778</v>
+        <v>90791</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,6 +1779,11 @@
       </c>
       <c r="E11" t="n">
         <v>5447</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1815,10 +1877,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122330362</v>
+        <v>122330337</v>
       </c>
       <c r="B12" t="n">
-        <v>57395</v>
+        <v>5193</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,15 +1889,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>105930</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1843,16 +1910,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1862,10 +1926,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650925</v>
+        <v>650804</v>
       </c>
       <c r="R12" t="n">
-        <v>6673848</v>
+        <v>6673534</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1897,7 +1961,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1971,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,10 +1998,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122330337</v>
+        <v>122330332</v>
       </c>
       <c r="B13" t="n">
-        <v>5193</v>
+        <v>5173</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,16 +2014,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100526</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1968,7 +2037,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1978,10 +2047,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650804</v>
+        <v>650886</v>
       </c>
       <c r="R13" t="n">
-        <v>6673534</v>
+        <v>6673750</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2013,7 +2082,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2092,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,10 +2119,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122330531</v>
+        <v>122330359</v>
       </c>
       <c r="B14" t="n">
-        <v>98211</v>
+        <v>57399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,34 +2131,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2097,10 +2171,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650980</v>
+        <v>650923</v>
       </c>
       <c r="R14" t="n">
-        <v>6673689</v>
+        <v>6673842</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2132,7 +2206,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2216,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,7 +2246,7 @@
         <v>122330407</v>
       </c>
       <c r="B15" t="n">
-        <v>91426</v>
+        <v>91439</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,6 +2260,11 @@
       </c>
       <c r="E15" t="n">
         <v>1339</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2279,10 +2358,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330329</v>
+        <v>122330384</v>
       </c>
       <c r="B16" t="n">
-        <v>5172</v>
+        <v>80613</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2295,27 +2374,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102204</v>
+        <v>1049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2323,10 +2401,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650881</v>
+        <v>650810</v>
       </c>
       <c r="R16" t="n">
-        <v>6673739</v>
+        <v>6673516</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2358,7 +2436,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2368,7 +2446,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,10 +2478,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122330545</v>
+        <v>122330403</v>
       </c>
       <c r="B17" t="n">
-        <v>98211</v>
+        <v>90826</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2407,34 +2490,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2442,10 +2521,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650988</v>
+        <v>650925</v>
       </c>
       <c r="R17" t="n">
-        <v>6673679</v>
+        <v>6673688</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2477,7 +2556,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2566,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,10 +2593,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122330403</v>
+        <v>122330531</v>
       </c>
       <c r="B18" t="n">
-        <v>90813</v>
+        <v>98224</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2526,25 +2605,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2552,10 +2645,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650925</v>
+        <v>650980</v>
       </c>
       <c r="R18" t="n">
-        <v>6673688</v>
+        <v>6673689</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2587,7 +2680,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2690,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,10 +2717,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330354</v>
+        <v>122330390</v>
       </c>
       <c r="B19" t="n">
-        <v>57395</v>
+        <v>90791</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,34 +2729,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2671,10 +2760,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650939</v>
+        <v>650923</v>
       </c>
       <c r="R19" t="n">
-        <v>6673581</v>
+        <v>6673571</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2706,7 +2795,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,7 +2805,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,10 +2832,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330401</v>
+        <v>122330551</v>
       </c>
       <c r="B20" t="n">
-        <v>90813</v>
+        <v>100490</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2755,25 +2844,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2781,10 +2876,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650967</v>
+        <v>650872</v>
       </c>
       <c r="R20" t="n">
-        <v>6673588</v>
+        <v>6673787</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2816,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2826,7 +2921,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2853,10 +2948,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122330356</v>
+        <v>122330362</v>
       </c>
       <c r="B21" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2870,6 +2965,11 @@
       </c>
       <c r="E21" t="n">
         <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2900,10 +3000,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650930</v>
+        <v>650925</v>
       </c>
       <c r="R21" t="n">
-        <v>6673590</v>
+        <v>6673848</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2935,7 +3035,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2945,7 +3045,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,7 +3075,7 @@
         <v>122330557</v>
       </c>
       <c r="B22" t="n">
-        <v>105317</v>
+        <v>105330</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2989,6 +3089,11 @@
       </c>
       <c r="E22" t="n">
         <v>221144</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122330545</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330401</v>
+        <v>122330551</v>
       </c>
       <c r="B3" t="n">
-        <v>90826</v>
+        <v>100503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650967</v>
+        <v>650872</v>
       </c>
       <c r="R3" t="n">
-        <v>6673588</v>
+        <v>6673787</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330547</v>
+        <v>122330550</v>
       </c>
       <c r="B4" t="n">
-        <v>98224</v>
+        <v>100503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,37 +927,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -966,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650902</v>
+        <v>650914</v>
       </c>
       <c r="R4" t="n">
-        <v>6673754</v>
+        <v>6673702</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1001,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330356</v>
+        <v>122330359</v>
       </c>
       <c r="B5" t="n">
         <v>57399</v>
@@ -1080,7 +1073,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1090,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650930</v>
+        <v>650923</v>
       </c>
       <c r="R5" t="n">
-        <v>6673590</v>
+        <v>6673842</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1125,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330352</v>
+        <v>122330396</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>90804</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,39 +1167,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1214,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650928</v>
+        <v>650952</v>
       </c>
       <c r="R6" t="n">
-        <v>6673572</v>
+        <v>6673856</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1249,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1259,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330550</v>
+        <v>122330547</v>
       </c>
       <c r="B7" t="n">
-        <v>100490</v>
+        <v>98237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,29 +1282,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1330,10 +1322,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650914</v>
+        <v>650902</v>
       </c>
       <c r="R7" t="n">
-        <v>6673702</v>
+        <v>6673754</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1365,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1367,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122330354</v>
+        <v>122330384</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,35 +1410,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1454,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650939</v>
+        <v>650810</v>
       </c>
       <c r="R8" t="n">
-        <v>6673581</v>
+        <v>6673516</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1489,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1499,7 +1482,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330329</v>
+        <v>122330362</v>
       </c>
       <c r="B9" t="n">
-        <v>5172</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,30 +1530,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102204</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1575,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650881</v>
+        <v>650925</v>
       </c>
       <c r="R9" t="n">
-        <v>6673739</v>
+        <v>6673848</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1610,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,7 +1611,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,10 +1638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330380</v>
+        <v>122330407</v>
       </c>
       <c r="B10" t="n">
-        <v>74696</v>
+        <v>91452</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1663,21 +1654,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1690,10 +1681,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650859</v>
+        <v>650944</v>
       </c>
       <c r="R10" t="n">
-        <v>6673800</v>
+        <v>6673706</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1725,7 +1716,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1735,7 +1726,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,10 +1753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330396</v>
+        <v>122330354</v>
       </c>
       <c r="B11" t="n">
-        <v>90791</v>
+        <v>57399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1774,30 +1765,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650952</v>
+        <v>650939</v>
       </c>
       <c r="R11" t="n">
-        <v>6673856</v>
+        <v>6673581</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2119,10 +2119,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122330359</v>
+        <v>122330329</v>
       </c>
       <c r="B14" t="n">
-        <v>57399</v>
+        <v>5172</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,33 +2135,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>102204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2171,10 +2168,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650923</v>
+        <v>650881</v>
       </c>
       <c r="R14" t="n">
-        <v>6673842</v>
+        <v>6673739</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2206,7 +2203,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2216,7 +2213,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,10 +2240,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122330407</v>
+        <v>122330356</v>
       </c>
       <c r="B15" t="n">
-        <v>91439</v>
+        <v>57399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2255,30 +2252,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2286,10 +2292,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650944</v>
+        <v>650930</v>
       </c>
       <c r="R15" t="n">
-        <v>6673706</v>
+        <v>6673590</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2321,7 +2327,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2331,7 +2337,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2358,10 +2364,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330384</v>
+        <v>122330352</v>
       </c>
       <c r="B16" t="n">
-        <v>80613</v>
+        <v>57399</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2374,26 +2380,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2401,10 +2416,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650810</v>
+        <v>650928</v>
       </c>
       <c r="R16" t="n">
-        <v>6673516</v>
+        <v>6673572</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2436,7 +2451,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2446,12 +2461,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2478,10 +2488,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122330403</v>
+        <v>122330390</v>
       </c>
       <c r="B17" t="n">
-        <v>90826</v>
+        <v>90804</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2490,25 +2500,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2521,10 +2531,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650925</v>
+        <v>650923</v>
       </c>
       <c r="R17" t="n">
-        <v>6673688</v>
+        <v>6673571</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2556,7 +2566,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2566,7 +2576,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2593,10 +2603,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122330531</v>
+        <v>122330403</v>
       </c>
       <c r="B18" t="n">
-        <v>98224</v>
+        <v>90839</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2605,39 +2615,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2645,10 +2646,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650980</v>
+        <v>650925</v>
       </c>
       <c r="R18" t="n">
-        <v>6673689</v>
+        <v>6673688</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2680,7 +2681,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2690,7 +2691,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2717,10 +2718,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330390</v>
+        <v>122330531</v>
       </c>
       <c r="B19" t="n">
-        <v>90791</v>
+        <v>98237</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2729,30 +2730,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2760,10 +2770,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650923</v>
+        <v>650980</v>
       </c>
       <c r="R19" t="n">
-        <v>6673571</v>
+        <v>6673689</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2795,7 +2805,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2805,7 +2815,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2832,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330551</v>
+        <v>122330380</v>
       </c>
       <c r="B20" t="n">
-        <v>100490</v>
+        <v>74696</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2848,27 +2858,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2876,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650872</v>
+        <v>650859</v>
       </c>
       <c r="R20" t="n">
-        <v>6673787</v>
+        <v>6673800</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2911,7 +2920,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,7 +2930,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2948,10 +2957,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122330362</v>
+        <v>122330401</v>
       </c>
       <c r="B21" t="n">
-        <v>57399</v>
+        <v>90839</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2964,35 +2973,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650925</v>
+        <v>650967</v>
       </c>
       <c r="R21" t="n">
-        <v>6673848</v>
+        <v>6673588</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3075,7 +3075,7 @@
         <v>122330557</v>
       </c>
       <c r="B22" t="n">
-        <v>105330</v>
+        <v>105343</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -1638,10 +1638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330407</v>
+        <v>122330354</v>
       </c>
       <c r="B10" t="n">
-        <v>91452</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1650,30 +1650,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1681,10 +1690,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650944</v>
+        <v>650939</v>
       </c>
       <c r="R10" t="n">
-        <v>6673706</v>
+        <v>6673581</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1716,7 +1725,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1726,7 +1735,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,10 +1762,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330354</v>
+        <v>122330407</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>91452</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1765,39 +1774,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650939</v>
+        <v>650944</v>
       </c>
       <c r="R11" t="n">
-        <v>6673581</v>
+        <v>6673706</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330545</v>
+        <v>122330403</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>90839</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650988</v>
+        <v>650925</v>
       </c>
       <c r="R2" t="n">
-        <v>6673679</v>
+        <v>6673688</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330551</v>
+        <v>122330352</v>
       </c>
       <c r="B3" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,31 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650872</v>
+        <v>650928</v>
       </c>
       <c r="R3" t="n">
-        <v>6673787</v>
+        <v>6673572</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330550</v>
+        <v>122330545</v>
       </c>
       <c r="B4" t="n">
-        <v>100503</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,29 +926,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -959,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650914</v>
+        <v>650988</v>
       </c>
       <c r="R4" t="n">
-        <v>6673702</v>
+        <v>6673679</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -994,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330359</v>
+        <v>122330332</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,37 +1050,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1083,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650923</v>
+        <v>650886</v>
       </c>
       <c r="R5" t="n">
-        <v>6673842</v>
+        <v>6673750</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1118,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330396</v>
+        <v>122330551</v>
       </c>
       <c r="B6" t="n">
-        <v>90804</v>
+        <v>100503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,26 +1175,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1198,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650952</v>
+        <v>650872</v>
       </c>
       <c r="R6" t="n">
-        <v>6673856</v>
+        <v>6673787</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1233,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330547</v>
+        <v>122330531</v>
       </c>
       <c r="B7" t="n">
         <v>98237</v>
@@ -1305,7 +1310,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1322,10 +1327,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650902</v>
+        <v>650980</v>
       </c>
       <c r="R7" t="n">
-        <v>6673754</v>
+        <v>6673689</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1357,7 +1362,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,7 +1372,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122330384</v>
+        <v>122330547</v>
       </c>
       <c r="B8" t="n">
-        <v>80613</v>
+        <v>98237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,30 +1411,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1437,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650810</v>
+        <v>650902</v>
       </c>
       <c r="R8" t="n">
-        <v>6673516</v>
+        <v>6673754</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1472,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,12 +1496,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330362</v>
+        <v>122330329</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>5172</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,33 +1539,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>102204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1566,10 +1572,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650925</v>
+        <v>650881</v>
       </c>
       <c r="R9" t="n">
-        <v>6673848</v>
+        <v>6673739</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1601,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1617,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,10 +1644,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330354</v>
+        <v>122330550</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1650,39 +1656,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1690,10 +1688,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650939</v>
+        <v>650914</v>
       </c>
       <c r="R10" t="n">
-        <v>6673581</v>
+        <v>6673702</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1725,7 +1723,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1735,7 +1733,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330407</v>
+        <v>122330337</v>
       </c>
       <c r="B11" t="n">
-        <v>91452</v>
+        <v>5193</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1778,26 +1776,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1339</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1805,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650944</v>
+        <v>650804</v>
       </c>
       <c r="R11" t="n">
-        <v>6673706</v>
+        <v>6673534</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1840,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1850,7 +1854,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1877,10 +1881,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122330337</v>
+        <v>122330354</v>
       </c>
       <c r="B12" t="n">
-        <v>5193</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1889,20 +1893,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1910,13 +1914,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1926,10 +1933,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650804</v>
+        <v>650939</v>
       </c>
       <c r="R12" t="n">
-        <v>6673534</v>
+        <v>6673581</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1961,7 +1968,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1971,7 +1978,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1998,10 +2005,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122330332</v>
+        <v>122330407</v>
       </c>
       <c r="B13" t="n">
-        <v>5173</v>
+        <v>91452</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2014,32 +2021,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>1339</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2047,10 +2048,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650886</v>
+        <v>650944</v>
       </c>
       <c r="R13" t="n">
-        <v>6673750</v>
+        <v>6673706</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2082,7 +2083,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2092,7 +2093,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,10 +2120,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122330329</v>
+        <v>122330380</v>
       </c>
       <c r="B14" t="n">
-        <v>5172</v>
+        <v>74696</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2131,36 +2132,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102204</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2168,10 +2163,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650881</v>
+        <v>650859</v>
       </c>
       <c r="R14" t="n">
-        <v>6673739</v>
+        <v>6673800</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2203,7 +2198,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2213,7 +2208,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2240,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122330356</v>
+        <v>122330390</v>
       </c>
       <c r="B15" t="n">
-        <v>57399</v>
+        <v>90804</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2252,39 +2247,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2292,10 +2278,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650930</v>
+        <v>650923</v>
       </c>
       <c r="R15" t="n">
-        <v>6673590</v>
+        <v>6673571</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2327,7 +2313,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2337,7 +2323,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2364,10 +2350,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330352</v>
+        <v>122330384</v>
       </c>
       <c r="B16" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2380,35 +2366,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2416,10 +2393,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650928</v>
+        <v>650810</v>
       </c>
       <c r="R16" t="n">
-        <v>6673572</v>
+        <v>6673516</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2451,7 +2428,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2461,7 +2438,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2488,10 +2470,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122330390</v>
+        <v>122330401</v>
       </c>
       <c r="B17" t="n">
-        <v>90804</v>
+        <v>90839</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2500,25 +2482,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2531,10 +2513,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650923</v>
+        <v>650967</v>
       </c>
       <c r="R17" t="n">
-        <v>6673571</v>
+        <v>6673588</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2566,7 +2548,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2576,7 +2558,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2603,10 +2585,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122330403</v>
+        <v>122330396</v>
       </c>
       <c r="B18" t="n">
-        <v>90839</v>
+        <v>90804</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,25 +2597,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2646,10 +2628,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650925</v>
+        <v>650952</v>
       </c>
       <c r="R18" t="n">
-        <v>6673688</v>
+        <v>6673856</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2681,7 +2663,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2691,7 +2673,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2718,10 +2700,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330531</v>
+        <v>122330359</v>
       </c>
       <c r="B19" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2730,39 +2712,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2770,10 +2752,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650980</v>
+        <v>650923</v>
       </c>
       <c r="R19" t="n">
-        <v>6673689</v>
+        <v>6673842</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2805,7 +2787,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2815,7 +2797,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,10 +2824,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330380</v>
+        <v>122330356</v>
       </c>
       <c r="B20" t="n">
-        <v>74696</v>
+        <v>57399</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2854,30 +2836,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2885,10 +2876,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650859</v>
+        <v>650930</v>
       </c>
       <c r="R20" t="n">
-        <v>6673800</v>
+        <v>6673590</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2920,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2930,7 +2921,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2957,10 +2948,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122330401</v>
+        <v>122330362</v>
       </c>
       <c r="B21" t="n">
-        <v>90839</v>
+        <v>57399</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2973,26 +2964,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650967</v>
+        <v>650925</v>
       </c>
       <c r="R21" t="n">
-        <v>6673588</v>
+        <v>6673848</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -2005,10 +2005,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122330407</v>
+        <v>122330380</v>
       </c>
       <c r="B13" t="n">
-        <v>91452</v>
+        <v>74696</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2021,21 +2021,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1339</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650944</v>
+        <v>650859</v>
       </c>
       <c r="R13" t="n">
-        <v>6673706</v>
+        <v>6673800</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2120,10 +2120,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122330380</v>
+        <v>122330407</v>
       </c>
       <c r="B14" t="n">
-        <v>74696</v>
+        <v>91452</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2136,21 +2136,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650859</v>
+        <v>650944</v>
       </c>
       <c r="R14" t="n">
-        <v>6673800</v>
+        <v>6673706</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330403</v>
+        <v>122330384</v>
       </c>
       <c r="B2" t="n">
-        <v>90839</v>
+        <v>80613</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650925</v>
+        <v>650810</v>
       </c>
       <c r="R2" t="n">
-        <v>6673688</v>
+        <v>6673516</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330352</v>
+        <v>122330354</v>
       </c>
       <c r="B3" t="n">
         <v>57399</v>
@@ -832,7 +837,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650928</v>
+        <v>650939</v>
       </c>
       <c r="R3" t="n">
-        <v>6673572</v>
+        <v>6673581</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330545</v>
+        <v>122330547</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,12 +954,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -966,10 +971,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650988</v>
+        <v>650902</v>
       </c>
       <c r="R4" t="n">
-        <v>6673679</v>
+        <v>6673754</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1001,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330332</v>
+        <v>122330337</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>5193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,21 +1059,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1077,7 +1082,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1087,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650886</v>
+        <v>650804</v>
       </c>
       <c r="R5" t="n">
-        <v>6673750</v>
+        <v>6673534</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1122,7 +1127,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1137,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330551</v>
+        <v>122330352</v>
       </c>
       <c r="B6" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,31 +1176,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1203,10 +1216,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650872</v>
+        <v>650928</v>
       </c>
       <c r="R6" t="n">
-        <v>6673787</v>
+        <v>6673572</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1238,7 +1251,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1261,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330531</v>
+        <v>122330380</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>74696</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,39 +1300,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1327,10 +1331,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650980</v>
+        <v>650859</v>
       </c>
       <c r="R7" t="n">
-        <v>6673689</v>
+        <v>6673800</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1362,7 +1366,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1372,7 +1376,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122330547</v>
+        <v>122330531</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1434,7 +1438,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1451,10 +1455,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650902</v>
+        <v>650980</v>
       </c>
       <c r="R8" t="n">
-        <v>6673754</v>
+        <v>6673689</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1486,7 +1490,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1500,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330329</v>
+        <v>122330401</v>
       </c>
       <c r="B9" t="n">
-        <v>5172</v>
+        <v>90833</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,32 +1543,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102204</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1572,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650881</v>
+        <v>650967</v>
       </c>
       <c r="R9" t="n">
-        <v>6673739</v>
+        <v>6673588</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1607,7 +1605,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1615,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,10 +1642,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330550</v>
+        <v>122330551</v>
       </c>
       <c r="B10" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1688,10 +1686,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650914</v>
+        <v>650872</v>
       </c>
       <c r="R10" t="n">
-        <v>6673702</v>
+        <v>6673787</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1723,7 +1721,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1733,7 +1731,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,10 +1758,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330337</v>
+        <v>122330407</v>
       </c>
       <c r="B11" t="n">
-        <v>5193</v>
+        <v>91453</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,32 +1774,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1809,10 +1801,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650804</v>
+        <v>650944</v>
       </c>
       <c r="R11" t="n">
-        <v>6673534</v>
+        <v>6673706</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1844,7 +1836,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1846,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,7 +1873,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122330354</v>
+        <v>122330359</v>
       </c>
       <c r="B12" t="n">
         <v>57399</v>
@@ -1923,7 +1915,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1933,10 +1925,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650939</v>
+        <v>650923</v>
       </c>
       <c r="R12" t="n">
-        <v>6673581</v>
+        <v>6673842</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1968,7 +1960,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1978,7 +1970,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2005,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122330380</v>
+        <v>122330545</v>
       </c>
       <c r="B13" t="n">
-        <v>74696</v>
+        <v>98240</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2017,30 +2009,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2048,10 +2049,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650859</v>
+        <v>650988</v>
       </c>
       <c r="R13" t="n">
-        <v>6673800</v>
+        <v>6673679</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2083,7 +2084,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2093,7 +2094,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2120,10 +2121,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122330407</v>
+        <v>122330362</v>
       </c>
       <c r="B14" t="n">
-        <v>91452</v>
+        <v>57399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2132,30 +2133,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2163,10 +2173,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650944</v>
+        <v>650925</v>
       </c>
       <c r="R14" t="n">
-        <v>6673706</v>
+        <v>6673848</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2198,7 +2208,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2208,7 +2218,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2235,10 +2245,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122330390</v>
+        <v>122330356</v>
       </c>
       <c r="B15" t="n">
-        <v>90804</v>
+        <v>57399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,30 +2257,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2278,10 +2297,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650923</v>
+        <v>650930</v>
       </c>
       <c r="R15" t="n">
-        <v>6673571</v>
+        <v>6673590</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2313,7 +2332,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2323,7 +2342,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,10 +2369,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330384</v>
+        <v>122330329</v>
       </c>
       <c r="B16" t="n">
-        <v>80613</v>
+        <v>5172</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,26 +2385,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>102204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2393,10 +2418,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650810</v>
+        <v>650881</v>
       </c>
       <c r="R16" t="n">
-        <v>6673516</v>
+        <v>6673739</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2428,7 +2453,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2438,12 +2463,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,10 +2490,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122330401</v>
+        <v>122330403</v>
       </c>
       <c r="B17" t="n">
-        <v>90839</v>
+        <v>90833</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2513,10 +2533,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650967</v>
+        <v>650925</v>
       </c>
       <c r="R17" t="n">
-        <v>6673588</v>
+        <v>6673688</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2548,7 +2568,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2558,7 +2578,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2585,10 +2605,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122330396</v>
+        <v>122330332</v>
       </c>
       <c r="B18" t="n">
-        <v>90804</v>
+        <v>5173</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2601,26 +2621,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2628,10 +2654,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650952</v>
+        <v>650886</v>
       </c>
       <c r="R18" t="n">
-        <v>6673856</v>
+        <v>6673750</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2663,7 +2689,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2673,7 +2699,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2700,10 +2726,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330359</v>
+        <v>122330396</v>
       </c>
       <c r="B19" t="n">
-        <v>57399</v>
+        <v>90798</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2712,39 +2738,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2752,10 +2769,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650923</v>
+        <v>650952</v>
       </c>
       <c r="R19" t="n">
-        <v>6673842</v>
+        <v>6673856</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2787,7 +2804,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2797,7 +2814,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2824,10 +2841,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330356</v>
+        <v>122330390</v>
       </c>
       <c r="B20" t="n">
-        <v>57399</v>
+        <v>90798</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2836,39 +2853,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2876,10 +2884,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650930</v>
+        <v>650923</v>
       </c>
       <c r="R20" t="n">
-        <v>6673590</v>
+        <v>6673571</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2911,7 +2919,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,7 +2929,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2948,10 +2956,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122330362</v>
+        <v>122330550</v>
       </c>
       <c r="B21" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2960,39 +2968,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650925</v>
+        <v>650914</v>
       </c>
       <c r="R21" t="n">
-        <v>6673848</v>
+        <v>6673702</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3075,7 +3075,7 @@
         <v>122330557</v>
       </c>
       <c r="B22" t="n">
-        <v>105343</v>
+        <v>105346</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330384</v>
+        <v>122330329</v>
       </c>
       <c r="B2" t="n">
-        <v>80613</v>
+        <v>5172</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1049</v>
+        <v>102204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650810</v>
+        <v>650881</v>
       </c>
       <c r="R2" t="n">
-        <v>6673516</v>
+        <v>6673739</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330354</v>
+        <v>122330550</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,39 +808,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650939</v>
+        <v>650914</v>
       </c>
       <c r="R3" t="n">
-        <v>6673581</v>
+        <v>6673702</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -882,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330547</v>
+        <v>122330403</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>90833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,39 +924,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -971,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650902</v>
+        <v>650925</v>
       </c>
       <c r="R4" t="n">
-        <v>6673754</v>
+        <v>6673688</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1006,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330337</v>
+        <v>122330359</v>
       </c>
       <c r="B5" t="n">
-        <v>5193</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,20 +1039,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1076,13 +1060,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1092,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650804</v>
+        <v>650923</v>
       </c>
       <c r="R5" t="n">
-        <v>6673534</v>
+        <v>6673842</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1127,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1137,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330352</v>
+        <v>122330337</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,20 +1163,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1197,16 +1184,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1216,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650928</v>
+        <v>650804</v>
       </c>
       <c r="R6" t="n">
-        <v>6673572</v>
+        <v>6673534</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1251,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1261,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330380</v>
+        <v>122330332</v>
       </c>
       <c r="B7" t="n">
-        <v>74696</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,26 +1288,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1331,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650859</v>
+        <v>650886</v>
       </c>
       <c r="R7" t="n">
-        <v>6673800</v>
+        <v>6673750</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1366,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1376,7 +1366,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,7 +1393,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122330531</v>
+        <v>122330545</v>
       </c>
       <c r="B8" t="n">
         <v>98240</v>
@@ -1438,12 +1428,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1455,10 +1445,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650980</v>
+        <v>650988</v>
       </c>
       <c r="R8" t="n">
-        <v>6673689</v>
+        <v>6673679</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1490,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1500,7 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330401</v>
+        <v>122330407</v>
       </c>
       <c r="B9" t="n">
-        <v>90833</v>
+        <v>91453</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,25 +1529,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1570,10 +1560,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650967</v>
+        <v>650944</v>
       </c>
       <c r="R9" t="n">
-        <v>6673588</v>
+        <v>6673706</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1605,7 +1595,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1615,7 +1605,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330551</v>
+        <v>122330354</v>
       </c>
       <c r="B10" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1654,31 +1644,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1686,10 +1684,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650872</v>
+        <v>650939</v>
       </c>
       <c r="R10" t="n">
-        <v>6673787</v>
+        <v>6673581</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1721,7 +1719,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1731,7 +1729,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,10 +1756,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330407</v>
+        <v>122330547</v>
       </c>
       <c r="B11" t="n">
-        <v>91453</v>
+        <v>98240</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1770,30 +1768,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1801,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650944</v>
+        <v>650902</v>
       </c>
       <c r="R11" t="n">
-        <v>6673706</v>
+        <v>6673754</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1836,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1846,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1873,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122330359</v>
+        <v>122330396</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>90798</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,39 +1892,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1925,10 +1923,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650923</v>
+        <v>650952</v>
       </c>
       <c r="R12" t="n">
-        <v>6673842</v>
+        <v>6673856</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1960,7 +1958,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1970,7 +1968,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1997,10 +1995,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122330545</v>
+        <v>122330380</v>
       </c>
       <c r="B13" t="n">
-        <v>98240</v>
+        <v>74696</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2009,39 +2007,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2049,10 +2038,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650988</v>
+        <v>650859</v>
       </c>
       <c r="R13" t="n">
-        <v>6673679</v>
+        <v>6673800</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2084,7 +2073,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2094,7 +2083,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2245,10 +2234,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122330356</v>
+        <v>122330531</v>
       </c>
       <c r="B15" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2257,39 +2246,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2297,10 +2286,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650930</v>
+        <v>650980</v>
       </c>
       <c r="R15" t="n">
-        <v>6673590</v>
+        <v>6673689</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2332,7 +2321,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2342,7 +2331,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,10 +2358,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330329</v>
+        <v>122330390</v>
       </c>
       <c r="B16" t="n">
-        <v>5172</v>
+        <v>90798</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2381,36 +2370,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102204</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2418,10 +2401,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650881</v>
+        <v>650923</v>
       </c>
       <c r="R16" t="n">
-        <v>6673739</v>
+        <v>6673571</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2453,7 +2436,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2463,7 +2446,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,10 +2473,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122330403</v>
+        <v>122330384</v>
       </c>
       <c r="B17" t="n">
-        <v>90833</v>
+        <v>80613</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2506,21 +2489,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2533,10 +2516,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650925</v>
+        <v>650810</v>
       </c>
       <c r="R17" t="n">
-        <v>6673688</v>
+        <v>6673516</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2568,7 +2551,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2578,7 +2561,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2605,10 +2593,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122330332</v>
+        <v>122330401</v>
       </c>
       <c r="B18" t="n">
-        <v>5173</v>
+        <v>90833</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2617,36 +2605,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2654,10 +2636,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650886</v>
+        <v>650967</v>
       </c>
       <c r="R18" t="n">
-        <v>6673750</v>
+        <v>6673588</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2689,7 +2671,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2699,7 +2681,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2726,10 +2708,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330396</v>
+        <v>122330551</v>
       </c>
       <c r="B19" t="n">
-        <v>90798</v>
+        <v>100506</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2742,26 +2724,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2769,10 +2752,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650952</v>
+        <v>650872</v>
       </c>
       <c r="R19" t="n">
-        <v>6673856</v>
+        <v>6673787</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2804,7 +2787,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2814,7 +2797,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2841,10 +2824,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330390</v>
+        <v>122330356</v>
       </c>
       <c r="B20" t="n">
-        <v>90798</v>
+        <v>57399</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2853,30 +2836,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2884,10 +2876,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650923</v>
+        <v>650930</v>
       </c>
       <c r="R20" t="n">
-        <v>6673571</v>
+        <v>6673590</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2919,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2929,7 +2921,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2956,10 +2948,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122330550</v>
+        <v>122330352</v>
       </c>
       <c r="B21" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2968,31 +2960,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650914</v>
+        <v>650928</v>
       </c>
       <c r="R21" t="n">
-        <v>6673702</v>
+        <v>6673572</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330329</v>
+        <v>122330407</v>
       </c>
       <c r="B2" t="n">
-        <v>5172</v>
+        <v>91454</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102204</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650881</v>
+        <v>650944</v>
       </c>
       <c r="R2" t="n">
-        <v>6673739</v>
+        <v>6673706</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330550</v>
+        <v>122330354</v>
       </c>
       <c r="B3" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650914</v>
+        <v>650939</v>
       </c>
       <c r="R3" t="n">
-        <v>6673702</v>
+        <v>6673581</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -875,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330403</v>
+        <v>122330352</v>
       </c>
       <c r="B4" t="n">
-        <v>90833</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,26 +930,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650925</v>
+        <v>650928</v>
       </c>
       <c r="R4" t="n">
-        <v>6673688</v>
+        <v>6673572</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -990,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330359</v>
+        <v>122330551</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,39 +1050,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1079,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650923</v>
+        <v>650872</v>
       </c>
       <c r="R5" t="n">
-        <v>6673842</v>
+        <v>6673787</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1114,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330337</v>
+        <v>122330359</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,20 +1166,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1184,13 +1187,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1200,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650804</v>
+        <v>650923</v>
       </c>
       <c r="R6" t="n">
-        <v>6673534</v>
+        <v>6673842</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1235,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1251,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330332</v>
+        <v>122330547</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>98241</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,36 +1290,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1321,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650886</v>
+        <v>650902</v>
       </c>
       <c r="R7" t="n">
-        <v>6673750</v>
+        <v>6673754</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1356,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,7 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,7 +1405,7 @@
         <v>122330545</v>
       </c>
       <c r="B8" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1517,10 +1526,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330407</v>
+        <v>122330384</v>
       </c>
       <c r="B9" t="n">
-        <v>91453</v>
+        <v>80614</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,25 +1538,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1560,10 +1569,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650944</v>
+        <v>650810</v>
       </c>
       <c r="R9" t="n">
-        <v>6673706</v>
+        <v>6673516</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1595,7 +1604,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1605,7 +1614,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1632,10 +1646,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330354</v>
+        <v>122330403</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>90834</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,35 +1662,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1684,10 +1689,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650939</v>
+        <v>650925</v>
       </c>
       <c r="R10" t="n">
-        <v>6673581</v>
+        <v>6673688</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1719,7 +1724,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1729,7 +1734,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,10 +1761,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330547</v>
+        <v>122330390</v>
       </c>
       <c r="B11" t="n">
-        <v>98240</v>
+        <v>90799</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1768,39 +1773,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1808,10 +1804,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650902</v>
+        <v>650923</v>
       </c>
       <c r="R11" t="n">
-        <v>6673754</v>
+        <v>6673571</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1843,7 +1839,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,7 +1849,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,10 +1876,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122330396</v>
+        <v>122330550</v>
       </c>
       <c r="B12" t="n">
-        <v>90798</v>
+        <v>100507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1896,26 +1892,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1923,10 +1920,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650952</v>
+        <v>650914</v>
       </c>
       <c r="R12" t="n">
-        <v>6673856</v>
+        <v>6673702</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1958,7 +1955,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1968,7 +1965,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,10 +1992,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122330380</v>
+        <v>122330332</v>
       </c>
       <c r="B13" t="n">
-        <v>74696</v>
+        <v>5173</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2011,26 +2008,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2038,10 +2041,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650859</v>
+        <v>650886</v>
       </c>
       <c r="R13" t="n">
-        <v>6673800</v>
+        <v>6673750</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2073,7 +2076,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2083,7 +2086,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2113,7 +2116,7 @@
         <v>122330362</v>
       </c>
       <c r="B14" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2234,10 +2237,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122330531</v>
+        <v>122330380</v>
       </c>
       <c r="B15" t="n">
-        <v>98240</v>
+        <v>74697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2246,39 +2249,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2286,10 +2280,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650980</v>
+        <v>650859</v>
       </c>
       <c r="R15" t="n">
-        <v>6673689</v>
+        <v>6673800</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2321,7 +2315,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2331,7 +2325,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2358,10 +2352,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330390</v>
+        <v>122330337</v>
       </c>
       <c r="B16" t="n">
-        <v>90798</v>
+        <v>5193</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2374,26 +2368,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650923</v>
+        <v>650804</v>
       </c>
       <c r="R16" t="n">
-        <v>6673571</v>
+        <v>6673534</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2473,10 +2473,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122330384</v>
+        <v>122330329</v>
       </c>
       <c r="B17" t="n">
-        <v>80613</v>
+        <v>5172</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2489,26 +2489,32 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>102204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2516,10 +2522,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650810</v>
+        <v>650881</v>
       </c>
       <c r="R17" t="n">
-        <v>6673516</v>
+        <v>6673739</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2551,7 +2557,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2561,12 +2567,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2593,10 +2594,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122330401</v>
+        <v>122330531</v>
       </c>
       <c r="B18" t="n">
-        <v>90833</v>
+        <v>98241</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2605,30 +2606,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2636,10 +2646,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650967</v>
+        <v>650980</v>
       </c>
       <c r="R18" t="n">
-        <v>6673588</v>
+        <v>6673689</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2671,7 +2681,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2681,7 +2691,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2708,10 +2718,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330551</v>
+        <v>122330356</v>
       </c>
       <c r="B19" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2720,31 +2730,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2752,10 +2770,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650872</v>
+        <v>650930</v>
       </c>
       <c r="R19" t="n">
-        <v>6673787</v>
+        <v>6673590</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2787,7 +2805,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2797,7 +2815,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2824,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330356</v>
+        <v>122330396</v>
       </c>
       <c r="B20" t="n">
-        <v>57399</v>
+        <v>90799</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2836,39 +2854,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2876,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650930</v>
+        <v>650952</v>
       </c>
       <c r="R20" t="n">
-        <v>6673590</v>
+        <v>6673856</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2911,7 +2920,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2921,7 +2930,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2948,10 +2957,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122330352</v>
+        <v>122330401</v>
       </c>
       <c r="B21" t="n">
-        <v>57399</v>
+        <v>90834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2964,35 +2973,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650928</v>
+        <v>650967</v>
       </c>
       <c r="R21" t="n">
-        <v>6673572</v>
+        <v>6673588</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3075,7 +3075,7 @@
         <v>122330557</v>
       </c>
       <c r="B22" t="n">
-        <v>105346</v>
+        <v>105347</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -2237,10 +2237,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122330380</v>
+        <v>122330337</v>
       </c>
       <c r="B15" t="n">
-        <v>74697</v>
+        <v>5193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2253,26 +2253,32 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2280,10 +2286,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650859</v>
+        <v>650804</v>
       </c>
       <c r="R15" t="n">
-        <v>6673800</v>
+        <v>6673534</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2315,7 +2321,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2325,7 +2331,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2352,10 +2358,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330337</v>
+        <v>122330380</v>
       </c>
       <c r="B16" t="n">
-        <v>5193</v>
+        <v>74697</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2368,32 +2374,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650804</v>
+        <v>650859</v>
       </c>
       <c r="R16" t="n">
-        <v>6673534</v>
+        <v>6673800</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330407</v>
+        <v>122330332</v>
       </c>
       <c r="B2" t="n">
-        <v>91454</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650944</v>
+        <v>650886</v>
       </c>
       <c r="R2" t="n">
-        <v>6673706</v>
+        <v>6673750</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330354</v>
+        <v>122330551</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +808,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650939</v>
+        <v>650872</v>
       </c>
       <c r="R3" t="n">
-        <v>6673581</v>
+        <v>6673787</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330352</v>
+        <v>122330547</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,39 +924,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -966,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650928</v>
+        <v>650902</v>
       </c>
       <c r="R4" t="n">
-        <v>6673572</v>
+        <v>6673754</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1001,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330551</v>
+        <v>122330531</v>
       </c>
       <c r="B5" t="n">
-        <v>100507</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,29 +1048,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1082,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650872</v>
+        <v>650980</v>
       </c>
       <c r="R5" t="n">
-        <v>6673787</v>
+        <v>6673689</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1117,7 +1123,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1133,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330359</v>
+        <v>122330407</v>
       </c>
       <c r="B6" t="n">
-        <v>57400</v>
+        <v>91457</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,39 +1172,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1206,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650923</v>
+        <v>650944</v>
       </c>
       <c r="R6" t="n">
-        <v>6673842</v>
+        <v>6673706</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1241,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330547</v>
+        <v>122330401</v>
       </c>
       <c r="B7" t="n">
-        <v>98241</v>
+        <v>90837</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,39 +1287,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1330,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650902</v>
+        <v>650967</v>
       </c>
       <c r="R7" t="n">
-        <v>6673754</v>
+        <v>6673588</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1365,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1363,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,7 +1393,7 @@
         <v>122330545</v>
       </c>
       <c r="B8" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1526,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330384</v>
+        <v>122330359</v>
       </c>
       <c r="B9" t="n">
-        <v>80614</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,26 +1530,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1569,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650810</v>
+        <v>650923</v>
       </c>
       <c r="R9" t="n">
-        <v>6673516</v>
+        <v>6673842</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1604,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1614,12 +1611,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,10 +1638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330403</v>
+        <v>122330356</v>
       </c>
       <c r="B10" t="n">
-        <v>90834</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1662,26 +1654,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1689,10 +1690,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650925</v>
+        <v>650930</v>
       </c>
       <c r="R10" t="n">
-        <v>6673688</v>
+        <v>6673590</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1724,7 +1725,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1734,7 +1735,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1761,10 +1762,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330390</v>
+        <v>122330550</v>
       </c>
       <c r="B11" t="n">
-        <v>90799</v>
+        <v>100510</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1777,26 +1778,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1804,10 +1806,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650923</v>
+        <v>650914</v>
       </c>
       <c r="R11" t="n">
-        <v>6673571</v>
+        <v>6673702</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1839,7 +1841,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1849,7 +1851,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1876,10 +1878,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122330550</v>
+        <v>122330329</v>
       </c>
       <c r="B12" t="n">
-        <v>100507</v>
+        <v>5172</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1888,31 +1890,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>102204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1920,10 +1927,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650914</v>
+        <v>650881</v>
       </c>
       <c r="R12" t="n">
-        <v>6673702</v>
+        <v>6673739</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1955,7 +1962,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1965,7 +1972,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,10 +1999,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122330332</v>
+        <v>122330384</v>
       </c>
       <c r="B13" t="n">
-        <v>5173</v>
+        <v>80617</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2004,36 +2011,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2041,10 +2042,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650886</v>
+        <v>650810</v>
       </c>
       <c r="R13" t="n">
-        <v>6673750</v>
+        <v>6673516</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2076,7 +2077,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2086,7 +2087,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2113,10 +2119,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122330362</v>
+        <v>122330337</v>
       </c>
       <c r="B14" t="n">
-        <v>57400</v>
+        <v>5193</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2125,20 +2131,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2146,16 +2152,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2165,10 +2168,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650925</v>
+        <v>650804</v>
       </c>
       <c r="R14" t="n">
-        <v>6673848</v>
+        <v>6673534</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2200,7 +2203,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2210,7 +2213,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2237,10 +2240,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122330337</v>
+        <v>122330352</v>
       </c>
       <c r="B15" t="n">
-        <v>5193</v>
+        <v>57400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2249,20 +2252,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2270,13 +2273,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2286,10 +2292,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650804</v>
+        <v>650928</v>
       </c>
       <c r="R15" t="n">
-        <v>6673534</v>
+        <v>6673572</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2321,7 +2327,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2331,7 +2337,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2358,10 +2364,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330380</v>
+        <v>122330390</v>
       </c>
       <c r="B16" t="n">
-        <v>74697</v>
+        <v>90802</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2374,21 +2380,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2401,10 +2407,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650859</v>
+        <v>650923</v>
       </c>
       <c r="R16" t="n">
-        <v>6673800</v>
+        <v>6673571</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2436,7 +2442,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2446,7 +2452,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2473,10 +2479,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122330329</v>
+        <v>122330362</v>
       </c>
       <c r="B17" t="n">
-        <v>5172</v>
+        <v>57400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2489,30 +2495,33 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102204</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2522,10 +2531,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650881</v>
+        <v>650925</v>
       </c>
       <c r="R17" t="n">
-        <v>6673739</v>
+        <v>6673848</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2557,7 +2566,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2567,7 +2576,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2594,10 +2603,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122330531</v>
+        <v>122330396</v>
       </c>
       <c r="B18" t="n">
-        <v>98241</v>
+        <v>90802</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2606,39 +2615,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650980</v>
+        <v>650952</v>
       </c>
       <c r="R18" t="n">
-        <v>6673689</v>
+        <v>6673856</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2718,7 +2718,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330356</v>
+        <v>122330354</v>
       </c>
       <c r="B19" t="n">
         <v>57400</v>
@@ -2760,7 +2760,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650930</v>
+        <v>650939</v>
       </c>
       <c r="R19" t="n">
-        <v>6673590</v>
+        <v>6673581</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330396</v>
+        <v>122330403</v>
       </c>
       <c r="B20" t="n">
-        <v>90799</v>
+        <v>90837</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2854,25 +2854,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650952</v>
+        <v>650925</v>
       </c>
       <c r="R20" t="n">
-        <v>6673856</v>
+        <v>6673688</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2957,10 +2957,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122330401</v>
+        <v>122330380</v>
       </c>
       <c r="B21" t="n">
-        <v>90834</v>
+        <v>74700</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2969,25 +2969,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650967</v>
+        <v>650859</v>
       </c>
       <c r="R21" t="n">
-        <v>6673588</v>
+        <v>6673800</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3075,7 +3075,7 @@
         <v>122330557</v>
       </c>
       <c r="B22" t="n">
-        <v>105347</v>
+        <v>105350</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330332</v>
+        <v>122330403</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>90837</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650886</v>
+        <v>650925</v>
       </c>
       <c r="R2" t="n">
-        <v>6673750</v>
+        <v>6673688</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330551</v>
+        <v>122330332</v>
       </c>
       <c r="B3" t="n">
-        <v>100510</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,27 +806,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650872</v>
+        <v>650886</v>
       </c>
       <c r="R3" t="n">
-        <v>6673787</v>
+        <v>6673750</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -875,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330547</v>
+        <v>122330380</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>74700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,39 +923,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650902</v>
+        <v>650859</v>
       </c>
       <c r="R4" t="n">
-        <v>6673754</v>
+        <v>6673800</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -999,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330531</v>
+        <v>122330356</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,39 +1038,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650980</v>
+        <v>650930</v>
       </c>
       <c r="R5" t="n">
-        <v>6673689</v>
+        <v>6673590</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1123,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1133,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330407</v>
+        <v>122330531</v>
       </c>
       <c r="B6" t="n">
-        <v>91457</v>
+        <v>98244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,30 +1162,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1203,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650944</v>
+        <v>650980</v>
       </c>
       <c r="R6" t="n">
-        <v>6673706</v>
+        <v>6673689</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1238,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330401</v>
+        <v>122330407</v>
       </c>
       <c r="B7" t="n">
-        <v>90837</v>
+        <v>91457</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,25 +1286,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1318,10 +1317,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650967</v>
+        <v>650944</v>
       </c>
       <c r="R7" t="n">
-        <v>6673588</v>
+        <v>6673706</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1353,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122330545</v>
+        <v>122330401</v>
       </c>
       <c r="B8" t="n">
-        <v>98244</v>
+        <v>90837</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,39 +1401,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1442,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650988</v>
+        <v>650967</v>
       </c>
       <c r="R8" t="n">
-        <v>6673679</v>
+        <v>6673588</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1477,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,7 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1638,7 +1628,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330356</v>
+        <v>122330362</v>
       </c>
       <c r="B10" t="n">
         <v>57400</v>
@@ -1690,10 +1680,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650930</v>
+        <v>650925</v>
       </c>
       <c r="R10" t="n">
-        <v>6673590</v>
+        <v>6673848</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1725,7 +1715,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1735,7 +1725,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330550</v>
+        <v>122330396</v>
       </c>
       <c r="B11" t="n">
-        <v>100510</v>
+        <v>90802</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1778,27 +1768,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1806,10 +1795,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650914</v>
+        <v>650952</v>
       </c>
       <c r="R11" t="n">
-        <v>6673702</v>
+        <v>6673856</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1841,7 +1830,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1851,7 +1840,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1878,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122330329</v>
+        <v>122330547</v>
       </c>
       <c r="B12" t="n">
-        <v>5172</v>
+        <v>98244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1890,36 +1879,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102204</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1927,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650881</v>
+        <v>650902</v>
       </c>
       <c r="R12" t="n">
-        <v>6673739</v>
+        <v>6673754</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1962,7 +1954,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1972,7 +1964,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1999,10 +1991,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122330384</v>
+        <v>122330551</v>
       </c>
       <c r="B13" t="n">
-        <v>80617</v>
+        <v>100510</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2011,30 +2003,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2042,10 +2035,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650810</v>
+        <v>650872</v>
       </c>
       <c r="R13" t="n">
-        <v>6673516</v>
+        <v>6673787</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2077,7 +2070,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2087,12 +2080,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,10 +2107,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122330337</v>
+        <v>122330354</v>
       </c>
       <c r="B14" t="n">
-        <v>5193</v>
+        <v>57400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2131,20 +2119,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2152,13 +2140,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2168,10 +2159,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650804</v>
+        <v>650939</v>
       </c>
       <c r="R14" t="n">
-        <v>6673534</v>
+        <v>6673581</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2203,7 +2194,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2213,7 +2204,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2240,10 +2231,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122330352</v>
+        <v>122330550</v>
       </c>
       <c r="B15" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2252,39 +2243,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2292,10 +2275,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650928</v>
+        <v>650914</v>
       </c>
       <c r="R15" t="n">
-        <v>6673572</v>
+        <v>6673702</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2327,7 +2310,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2337,7 +2320,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2364,10 +2347,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330390</v>
+        <v>122330337</v>
       </c>
       <c r="B16" t="n">
-        <v>90802</v>
+        <v>5193</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2380,26 +2363,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2407,10 +2396,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650923</v>
+        <v>650804</v>
       </c>
       <c r="R16" t="n">
-        <v>6673571</v>
+        <v>6673534</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2442,7 +2431,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2452,7 +2441,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2479,10 +2468,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122330362</v>
+        <v>122330545</v>
       </c>
       <c r="B17" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2491,39 +2480,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2531,10 +2520,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650925</v>
+        <v>650988</v>
       </c>
       <c r="R17" t="n">
-        <v>6673848</v>
+        <v>6673679</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2566,7 +2555,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2576,7 +2565,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2603,7 +2592,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122330396</v>
+        <v>122330390</v>
       </c>
       <c r="B18" t="n">
         <v>90802</v>
@@ -2646,10 +2635,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650952</v>
+        <v>650923</v>
       </c>
       <c r="R18" t="n">
-        <v>6673856</v>
+        <v>6673571</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2681,7 +2670,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2691,7 +2680,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2718,7 +2707,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330354</v>
+        <v>122330352</v>
       </c>
       <c r="B19" t="n">
         <v>57400</v>
@@ -2760,7 +2749,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2770,10 +2759,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650939</v>
+        <v>650928</v>
       </c>
       <c r="R19" t="n">
-        <v>6673581</v>
+        <v>6673572</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2805,7 +2794,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2815,7 +2804,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,10 +2831,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330403</v>
+        <v>122330384</v>
       </c>
       <c r="B20" t="n">
-        <v>90837</v>
+        <v>80617</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2858,21 +2847,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2885,10 +2874,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650925</v>
+        <v>650810</v>
       </c>
       <c r="R20" t="n">
-        <v>6673688</v>
+        <v>6673516</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2920,7 +2909,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2930,7 +2919,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2957,10 +2951,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122330380</v>
+        <v>122330329</v>
       </c>
       <c r="B21" t="n">
-        <v>74700</v>
+        <v>5172</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2969,30 +2963,36 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>102204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>650859</v>
+        <v>650881</v>
       </c>
       <c r="R21" t="n">
-        <v>6673800</v>
+        <v>6673739</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -1628,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330362</v>
+        <v>122330396</v>
       </c>
       <c r="B10" t="n">
-        <v>57400</v>
+        <v>90802</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,39 +1640,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1680,10 +1671,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650925</v>
+        <v>650952</v>
       </c>
       <c r="R10" t="n">
-        <v>6673848</v>
+        <v>6673856</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1715,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1725,7 +1716,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330396</v>
+        <v>122330362</v>
       </c>
       <c r="B11" t="n">
-        <v>90802</v>
+        <v>57400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,30 +1755,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650952</v>
+        <v>650925</v>
       </c>
       <c r="R11" t="n">
-        <v>6673856</v>
+        <v>6673848</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -1628,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330396</v>
+        <v>122330362</v>
       </c>
       <c r="B10" t="n">
-        <v>90802</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,30 +1640,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1671,10 +1680,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650952</v>
+        <v>650925</v>
       </c>
       <c r="R10" t="n">
-        <v>6673856</v>
+        <v>6673848</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1706,7 +1715,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1725,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330362</v>
+        <v>122330396</v>
       </c>
       <c r="B11" t="n">
-        <v>57400</v>
+        <v>90802</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,39 +1764,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650925</v>
+        <v>650952</v>
       </c>
       <c r="R11" t="n">
-        <v>6673848</v>
+        <v>6673856</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2592,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122330390</v>
+        <v>122330352</v>
       </c>
       <c r="B18" t="n">
-        <v>90802</v>
+        <v>57400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2604,30 +2604,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2635,10 +2644,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650923</v>
+        <v>650928</v>
       </c>
       <c r="R18" t="n">
-        <v>6673571</v>
+        <v>6673572</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2670,7 +2679,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2680,7 +2689,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2707,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330352</v>
+        <v>122330390</v>
       </c>
       <c r="B19" t="n">
-        <v>57400</v>
+        <v>90802</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2719,39 +2728,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650928</v>
+        <v>650923</v>
       </c>
       <c r="R19" t="n">
-        <v>6673572</v>
+        <v>6673571</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122330403</v>
+        <v>122330384</v>
       </c>
       <c r="B2" t="n">
-        <v>90837</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650925</v>
+        <v>650810</v>
       </c>
       <c r="R2" t="n">
-        <v>6673688</v>
+        <v>6673516</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +758,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,48 +790,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122330332</v>
+        <v>122330401</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650886</v>
+        <v>650967</v>
       </c>
       <c r="R3" t="n">
-        <v>6673750</v>
+        <v>6673588</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -874,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,37 +900,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122330380</v>
+        <v>122330403</v>
       </c>
       <c r="B4" t="n">
-        <v>74700</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650859</v>
+        <v>650925</v>
       </c>
       <c r="R4" t="n">
-        <v>6673800</v>
+        <v>6673688</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,51 +1010,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122330356</v>
+        <v>122330406</v>
       </c>
       <c r="B5" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650930</v>
+        <v>650876</v>
       </c>
       <c r="R5" t="n">
-        <v>6673590</v>
+        <v>6673736</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1113,7 +1083,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1093,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,51 +1120,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122330531</v>
+        <v>122330407</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1202,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>650980</v>
+        <v>650944</v>
       </c>
       <c r="R6" t="n">
-        <v>6673689</v>
+        <v>6673706</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1237,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,15 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122330407</v>
+        <v>122330390</v>
       </c>
       <c r="B7" t="n">
-        <v>91457</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>650944</v>
+        <v>650923</v>
       </c>
       <c r="R7" t="n">
-        <v>6673706</v>
+        <v>6673571</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1352,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,37 +1340,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122330401</v>
+        <v>122330395</v>
       </c>
       <c r="B8" t="n">
-        <v>90837</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1432,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>650967</v>
+        <v>650956</v>
       </c>
       <c r="R8" t="n">
-        <v>6673588</v>
+        <v>6673811</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1467,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,51 +1450,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122330359</v>
+        <v>122330396</v>
       </c>
       <c r="B9" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1556,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>650923</v>
+        <v>650952</v>
       </c>
       <c r="R9" t="n">
-        <v>6673842</v>
+        <v>6673856</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1591,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1601,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,51 +1560,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122330362</v>
+        <v>122330398</v>
       </c>
       <c r="B10" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1680,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>650925</v>
+        <v>650877</v>
       </c>
       <c r="R10" t="n">
-        <v>6673848</v>
+        <v>6673728</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1715,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1725,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,37 +1670,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122330396</v>
+        <v>122330378</v>
       </c>
       <c r="B11" t="n">
-        <v>90802</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1795,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>650952</v>
+        <v>650851</v>
       </c>
       <c r="R11" t="n">
-        <v>6673856</v>
+        <v>6673834</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1830,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1840,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,51 +1780,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122330547</v>
+        <v>122330379</v>
       </c>
       <c r="B12" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1919,10 +1818,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>650902</v>
+        <v>650844</v>
       </c>
       <c r="R12" t="n">
-        <v>6673754</v>
+        <v>6673842</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1954,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1964,7 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,43 +1890,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122330551</v>
+        <v>122330380</v>
       </c>
       <c r="B13" t="n">
-        <v>100510</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2035,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>650872</v>
+        <v>650859</v>
       </c>
       <c r="R13" t="n">
-        <v>6673787</v>
+        <v>6673800</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2070,7 +1963,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2080,7 +1973,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,19 +2000,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122330354</v>
+        <v>122330352</v>
       </c>
       <c r="B14" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2149,7 +2037,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2159,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>650939</v>
+        <v>650928</v>
       </c>
       <c r="R14" t="n">
-        <v>6673581</v>
+        <v>6673572</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2194,7 +2082,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2204,7 +2092,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2231,15 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122330550</v>
+        <v>122330354</v>
       </c>
       <c r="B15" t="n">
-        <v>100510</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,27 +2130,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2275,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>650914</v>
+        <v>650939</v>
       </c>
       <c r="R15" t="n">
-        <v>6673702</v>
+        <v>6673581</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2310,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2320,7 +2211,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2347,15 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122330337</v>
+        <v>122330356</v>
       </c>
       <c r="B16" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,16 +2249,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2380,13 +2266,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2396,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>650804</v>
+        <v>650930</v>
       </c>
       <c r="R16" t="n">
-        <v>6673534</v>
+        <v>6673590</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2431,7 +2320,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2441,7 +2330,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2468,51 +2357,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122330545</v>
+        <v>122330359</v>
       </c>
       <c r="B17" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2520,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>650988</v>
+        <v>650923</v>
       </c>
       <c r="R17" t="n">
-        <v>6673679</v>
+        <v>6673842</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2555,7 +2439,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2565,7 +2449,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2592,19 +2476,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122330352</v>
+        <v>122330362</v>
       </c>
       <c r="B18" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2644,10 +2523,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>650928</v>
+        <v>650925</v>
       </c>
       <c r="R18" t="n">
-        <v>6673572</v>
+        <v>6673848</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2679,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2689,7 +2568,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2716,15 +2595,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122330390</v>
+        <v>122330332</v>
       </c>
       <c r="B19" t="n">
-        <v>90802</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,26 +2606,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2759,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>650923</v>
+        <v>650886</v>
       </c>
       <c r="R19" t="n">
-        <v>6673571</v>
+        <v>6673750</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2794,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2804,7 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2831,56 +2711,60 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122330384</v>
+        <v>86194984</v>
       </c>
       <c r="B20" t="n">
-        <v>80617</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>102118</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ackarebottnen, Upl</t>
+          <t>Vägen in mot Långmyren, Skyttorp-Knypplan, Upl 2274 m NE, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>650810</v>
+        <v>650865</v>
       </c>
       <c r="R20" t="n">
-        <v>6673516</v>
+        <v>6673921</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2904,27 +2788,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2020-06-12</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar inne i spricka, går inte att fota.</t>
+          <t>00:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2939,12 +2818,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Johan Södercrantz</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Johan Södercrantz</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2954,12 +2833,7 @@
         <v>122330329</v>
       </c>
       <c r="B21" t="n">
-        <v>5172</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3072,15 +2946,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122330557</v>
+        <v>122330337</v>
       </c>
       <c r="B22" t="n">
-        <v>105350</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3088,35 +2957,32 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3124,10 +2990,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>650896</v>
+        <v>650804</v>
       </c>
       <c r="R22" t="n">
-        <v>6673742</v>
+        <v>6673534</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3159,7 +3025,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3169,12 +3035,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Uppskattat antal.</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3183,7 +3044,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3199,6 +3059,826 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122330339</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ackarebottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>650958</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6673802</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122330531</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ackarebottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>650980</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6673689</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122330545</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ackarebottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>650988</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6673679</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122330547</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ackarebottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>650902</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6673754</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122330557</v>
+      </c>
+      <c r="B27" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ackarebottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>650896</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6673742</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Uppskattat antal.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122330550</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ackarebottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>650914</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6673702</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122330551</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ackarebottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>650872</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6673787</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 234-2025 artfynd.xlsx
+++ b/artfynd/A 234-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330384</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330401</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330403</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330406</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330407</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330390</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330395</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330396</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330398</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,6 +1827,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330378</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1887,6 +1942,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330379</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1997,6 +2057,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330380</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2116,6 +2181,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330352</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2235,6 +2305,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330354</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2354,6 +2429,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330356</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2473,6 +2553,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330359</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2592,6 +2677,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330362</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2708,6 +2798,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330332</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2827,6 +2922,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86194984</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2943,6 +3043,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330329</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3059,6 +3164,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330337</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3175,6 +3285,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330339</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3294,6 +3409,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330531</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3413,6 +3533,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330545</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3532,6 +3657,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330547</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3657,6 +3787,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330557</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3768,6 +3903,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330550</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3879,8 +4019,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122330551</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>